--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886336791528341</v>
+        <v>0.7886327812077328</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919477740075762</v>
+        <v>0.7919460381458538</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913106147639701</v>
+        <v>0.7913088561726833</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926897942748554</v>
+        <v>0.7926870069440951</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.79136386494703</v>
+        <v>0.7913609958317687</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899111994108823</v>
+        <v>0.7899082864796217</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883336737317718</v>
+        <v>0.7883307752670647</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872511343001255</v>
+        <v>0.7872482892377676</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892600000553843</v>
+        <v>0.7892566582224183</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945103219570094</v>
+        <v>0.7945087750998587</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969272309766031</v>
+        <v>0.7969255892230529</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993551669564641</v>
+        <v>0.7993534870936809</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001763759845602</v>
+        <v>0.8001755800714027</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986647353242048</v>
+        <v>0.7986652771322694</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992611931941652</v>
+        <v>0.7992622482110112</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039736149611081</v>
+        <v>0.803973088500347</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096299807514853</v>
+        <v>0.809627808275475</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.815803181494685</v>
+        <v>0.8158001925745092</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221940530137873</v>
+        <v>0.8221916608931631</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229431559433068</v>
+        <v>0.8229426454977556</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187744343876907</v>
+        <v>0.818776872973314</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153156048161968</v>
+        <v>0.8153189791948465</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139412179137802</v>
+        <v>0.8139474620771201</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123062206107836</v>
+        <v>0.8123162485988058</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8121611226759422</v>
+        <v>0.8121739522640525</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8173624013217091</v>
+        <v>0.8173781638791833</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.823054340467966</v>
+        <v>0.8230719358248776</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8299298339074388</v>
+        <v>0.8299493886623728</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8345993059971084</v>
+        <v>0.8346208548275181</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8197384688043204</v>
+        <v>0.8197632755313722</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.821561057341942</v>
+        <v>0.8215857950334865</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8089961888510718</v>
+        <v>0.8090232417130276</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8008857224757298</v>
+        <v>0.8009112228176309</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7936733442987838</v>
+        <v>0.7937027380250991</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7840853120124704</v>
+        <v>0.7841168223711029</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7686523282993578</v>
+        <v>0.7686647027698528</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664315913538526</v>
+        <v>0.7664401614011647</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758344426503717</v>
+        <v>0.7583446033391094</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7477112598597229</v>
+        <v>0.7476989489971383</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7388227033339727</v>
+        <v>0.7388030868585889</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7292527130622715</v>
+        <v>0.7292248918135587</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.733397600341807</v>
+        <v>0.7333518671403342</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7388032476446635</v>
+        <v>0.7387545431742668</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7483680596168849</v>
+        <v>0.748323757604614</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7571313470614811</v>
+        <v>0.7570883946239344</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7730731935299782</v>
+        <v>0.7730543695962171</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773924114381627</v>
+        <v>0.7773801362293242</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779493501011487</v>
+        <v>0.7779344870535412</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833284646389292</v>
+        <v>0.7833201350540293</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885718415502719</v>
+        <v>0.7885698017795526</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.792341296933206</v>
+        <v>0.7923420193204973</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893851388513292</v>
+        <v>0.789379339905701</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920399150880973</v>
+        <v>0.7920304471887174</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.797432106819053</v>
+        <v>0.7974155676521411</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.802516461147226</v>
+        <v>0.8024944996360754</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8051506162516848</v>
+        <v>0.8051289175750733</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077210220844842</v>
+        <v>0.8077020531170982</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099246535290764</v>
+        <v>0.8099095469718274</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096389110074076</v>
+        <v>0.8096351085202157</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088744646524717</v>
+        <v>0.8088811200616419</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8094756040661576</v>
+        <v>0.8094983565254417</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8099724661940074</v>
+        <v>0.8099887399897483</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.812371918090002</v>
+        <v>0.8123498704703893</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8165061065394854</v>
+        <v>0.8164456884406913</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8198029520302624</v>
+        <v>0.8197377837584411</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8231199429262185</v>
+        <v>0.8230635189344349</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8267270476713755</v>
+        <v>0.8266770441946962</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8292402151821664</v>
+        <v>0.8292009766510879</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8283228351233115</v>
+        <v>0.8283539553600324</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8264095950748641</v>
+        <v>0.8267035183939464</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8236096266921744</v>
+        <v>0.8240925752866636</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8197234376438181</v>
+        <v>0.8206143136153428</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.824890498768807</v>
+        <v>0.8258995111147749</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.830914653534756</v>
+        <v>0.830275766396535</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886327812077328</v>
+        <v>0.7886319021646219</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919460381458538</v>
+        <v>0.7919443387558986</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913088561726833</v>
+        <v>0.7913071342979235</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926870069440951</v>
+        <v>0.7926842779911832</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913609958317687</v>
+        <v>0.7913581868229134</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899082864796217</v>
+        <v>0.7899054345952081</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883307752670647</v>
+        <v>0.7883279375581455</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872482892377676</v>
+        <v>0.7872455038117789</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892566582224183</v>
+        <v>0.7892533862951673</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945087750998587</v>
+        <v>0.79450726079459</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969255892230529</v>
+        <v>0.7969239820485345</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993534870936809</v>
+        <v>0.7993518426413865</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001755800714027</v>
+        <v>0.8001748004946896</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986652771322694</v>
+        <v>0.7986658069933141</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992622482110112</v>
+        <v>0.7992632808389992</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803973088500347</v>
+        <v>0.8039725726578915</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.809627808275475</v>
+        <v>0.8096256802972699</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8158001925745092</v>
+        <v>0.8157972634465274</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221916608931631</v>
+        <v>0.8221893158408469</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229426454977556</v>
+        <v>0.8229421422747637</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818776872973314</v>
+        <v>0.8187792557373145</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153189791948465</v>
+        <v>0.8153222778855518</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139474620771201</v>
+        <v>0.8139535705061074</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123162485988058</v>
+        <v>0.8123260607271416</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8121739522640525</v>
+        <v>0.8121865074939189</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8173781638791833</v>
+        <v>0.8173935907848564</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8230719358248776</v>
+        <v>0.8230891581180044</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8299493886623728</v>
+        <v>0.8299685302447292</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8346208548275181</v>
+        <v>0.8346419593533975</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8197632755313722</v>
+        <v>0.8197875638981003</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8215857950334865</v>
+        <v>0.8216100169657639</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8090232417130276</v>
+        <v>0.8090497284749911</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8009112228176309</v>
+        <v>0.8009361910763458</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7937027380250991</v>
+        <v>0.7937315212034637</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7841168223711029</v>
+        <v>0.7841476844224297</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7686647027698528</v>
+        <v>0.7686768302067397</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664401614011647</v>
+        <v>0.7664485695191499</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583446033391094</v>
+        <v>0.7583447983074973</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476989489971383</v>
+        <v>0.7476869177558925</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7388030868585889</v>
+        <v>0.7387839066563834</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7292248918135587</v>
+        <v>0.7291976741107669</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7333518671403342</v>
+        <v>0.7333070890109987</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7387545431742668</v>
+        <v>0.7387068492568796</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.748323757604614</v>
+        <v>0.7482803635132173</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7570883946239344</v>
+        <v>0.7570463097744734</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7730543695962171</v>
+        <v>0.7730359242555518</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773801362293242</v>
+        <v>0.7773681028056404</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779344870535412</v>
+        <v>0.7779199192940043</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833201350540293</v>
+        <v>0.7833119723860702</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885698017795526</v>
+        <v>0.788567809536764</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923420193204973</v>
+        <v>0.7923427415128148</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789379339905701</v>
+        <v>0.7893736707297689</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920304471887174</v>
+        <v>0.7920211859436139</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7974155676521411</v>
+        <v>0.797399371941782</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8024944996360754</v>
+        <v>0.8024729845349896</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8051289175750733</v>
+        <v>0.8051076477585604</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8077020531170982</v>
+        <v>0.8076834376261324</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8099095469718274</v>
+        <v>0.8098947003022193</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096351085202157</v>
+        <v>0.8096313169104157</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088811200616419</v>
+        <v>0.8088875915415521</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8094983565254417</v>
+        <v>0.8095044186086322</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8099887399897483</v>
+        <v>0.8100415490684125</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8123498704703893</v>
+        <v>0.8123380683271776</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8164456884406913</v>
+        <v>0.8163592811912399</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8197377837584411</v>
+        <v>0.8196524442630184</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8230635189344349</v>
+        <v>0.8229795109650919</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8266770441946962</v>
+        <v>0.8265769429188372</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8292009766510879</v>
+        <v>0.8290854239363608</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8283539553600324</v>
+        <v>0.8282800947469385</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8267035183939464</v>
+        <v>0.826673375422655</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8240925752866636</v>
+        <v>0.8243287327989106</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8206143136153428</v>
+        <v>0.8211391739639293</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8258995111147749</v>
+        <v>0.8263695685761177</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,15 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.830275766396535</v>
+        <v>0.8309180630734065</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B81">
+        <v>0.8377236835615244</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886319021646219</v>
+        <v>0.788631041432901</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919443387558986</v>
+        <v>0.7919426747002981</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913071342979235</v>
+        <v>0.7913054480019132</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926842779911832</v>
+        <v>0.7926816056014463</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913581868229134</v>
+        <v>0.7913554360515797</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899054345952081</v>
+        <v>0.7899026418588213</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883279375581455</v>
+        <v>0.788325158714871</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872455038117789</v>
+        <v>0.7872427761668421</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892533862951673</v>
+        <v>0.78925018210346</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.79450726079459</v>
+        <v>0.7945057780245633</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969239820485345</v>
+        <v>0.7969224083721631</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993518426413865</v>
+        <v>0.7993502324918158</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001748004946896</v>
+        <v>0.8001740367571212</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986658069933141</v>
+        <v>0.7986663252971509</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992632808389992</v>
+        <v>0.7992642917829321</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039725726578915</v>
+        <v>0.803972067116634</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096256802972699</v>
+        <v>0.8096235954657651</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157972634465274</v>
+        <v>0.8157943923410553</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221893158408469</v>
+        <v>0.8221870164890666</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229421422747637</v>
+        <v>0.8229416461577739</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187792557373145</v>
+        <v>0.8187815845599904</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153222778855518</v>
+        <v>0.8153255033924892</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139535705061074</v>
+        <v>0.8139595475664054</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123260607271416</v>
+        <v>0.8123356638749271</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8121865074939189</v>
+        <v>0.8121987970526809</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8173935907848564</v>
+        <v>0.8174086926215844</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8230891581180044</v>
+        <v>0.8231060190576039</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8299685302447292</v>
+        <v>0.8299872715776099</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8346419593533975</v>
+        <v>0.8346626331573443</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8197875638981003</v>
+        <v>0.8198113499671018</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8216100169657639</v>
+        <v>0.8216337390844255</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8090497284749911</v>
+        <v>0.8090756666973579</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8009361910763458</v>
+        <v>0.8009606437077176</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7937315212034637</v>
+        <v>0.7937597126246165</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7841476844224297</v>
+        <v>0.7841779179173844</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7686768302067397</v>
+        <v>0.7686887178959654</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664485695191499</v>
+        <v>0.766456820183324</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583447983074973</v>
+        <v>0.7583450101668974</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476869177558925</v>
+        <v>0.7476751567846764</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7387839066563834</v>
+        <v>0.7387651484077954</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7291976741107669</v>
+        <v>0.7291710405798399</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7333070890109987</v>
+        <v>0.7332632363980143</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7387068492568796</v>
+        <v>0.7386601348322561</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7482803635132173</v>
+        <v>0.7482378497846353</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7570463097744734</v>
+        <v>0.7570050665686034</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7730359242555518</v>
+        <v>0.7730178462340402</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773681028056404</v>
+        <v>0.7773563041261579</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779199192940043</v>
+        <v>0.7779056381402855</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833119723860702</v>
+        <v>0.7833039716752885</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788567809536764</v>
+        <v>0.7885658631918435</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923427415128148</v>
+        <v>0.7923434630578499</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893736707297689</v>
+        <v>0.7893681270371788</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920211859436139</v>
+        <v>0.7920121246860002</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.797399371941782</v>
+        <v>0.7973835091502522</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8024729845349896</v>
+        <v>0.8024519024590122</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8051076477585604</v>
+        <v>0.8050867943482058</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8076834376261324</v>
+        <v>0.8076651660373082</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098947003022193</v>
+        <v>0.8098801071777035</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096313169104157</v>
+        <v>0.8096275378209661</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8088875915415521</v>
+        <v>0.808893885868688</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095044186086322</v>
+        <v>0.809510341051649</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8100415490684125</v>
+        <v>0.8099742610460903</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8123380683271776</v>
+        <v>0.8121802771923121</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8163592811912399</v>
+        <v>0.8160969311973278</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8196524442630184</v>
+        <v>0.8193965307344373</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8229795109650919</v>
+        <v>0.8226679991925598</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8265769429188372</v>
+        <v>0.8262273268778231</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8290854239363608</v>
+        <v>0.8286855433798309</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8282800947469385</v>
+        <v>0.8278793910366493</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.826673375422655</v>
+        <v>0.8262781544508978</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8243287327989106</v>
+        <v>0.8240932639868541</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8211391739639293</v>
+        <v>0.8210200871718686</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8263695685761177</v>
+        <v>0.8258932105816559</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8309180630734065</v>
+        <v>0.8298166353144366</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8377236835615244</v>
+        <v>0.8299856793546183</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788631041432901</v>
+        <v>0.7886301984463199</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919426747002981</v>
+        <v>0.7919410448884443</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913054480019132</v>
+        <v>0.791303796193395</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926816056014463</v>
+        <v>0.7926789880346384</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913554360515797</v>
+        <v>0.7913527417255541</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7899026418588213</v>
+        <v>0.7898999064495678</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788325158714871</v>
+        <v>0.7883224369246846</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872427761668421</v>
+        <v>0.7872401045237967</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.78925018210346</v>
+        <v>0.7892470435660111</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945057780245633</v>
+        <v>0.7945043258150308</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969224083721631</v>
+        <v>0.7969208671576313</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993502324918158</v>
+        <v>0.7993486555829262</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001740367571212</v>
+        <v>0.8001732883813559</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986663252971509</v>
+        <v>0.7986668324168549</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992642917829321</v>
+        <v>0.7992652817183521</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803972067116634</v>
+        <v>0.8039715715719302</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096235954657651</v>
+        <v>0.8096215524839154</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157943923410553</v>
+        <v>0.8157915775572777</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221870164890666</v>
+        <v>0.8221847615221956</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229416461577739</v>
+        <v>0.8229411570305769</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187815845599904</v>
+        <v>0.8187838612386735</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153255033924892</v>
+        <v>0.8153286581111019</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139595475664054</v>
+        <v>0.8139653974389293</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123356638749271</v>
+        <v>0.8123450646327078</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8121987970526809</v>
+        <v>0.8122108292653559</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8174086926215844</v>
+        <v>0.8174234795329584</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8231060190576039</v>
+        <v>0.8231225298700944</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8299872715776099</v>
+        <v>0.8300056250521227</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8346626331573443</v>
+        <v>0.8346828892746601</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8198113499671018</v>
+        <v>0.8198346491447922</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8216337390844255</v>
+        <v>0.8216569766852245</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8090756666973579</v>
+        <v>0.8091010732226556</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8009606437077176</v>
+        <v>0.800984596496978</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7937597126246165</v>
+        <v>0.7937873303175251</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7841779179173844</v>
+        <v>0.7842075418148581</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7686887178959654</v>
+        <v>0.7687003728413776</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.766456820183324</v>
+        <v>0.7664649177089712</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583450101668974</v>
+        <v>0.7583452377540134</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476751567846764</v>
+        <v>0.7476636571420027</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7387651484077954</v>
+        <v>0.7387467984103071</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7291710405798399</v>
+        <v>0.7291449726650123</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7332632363980143</v>
+        <v>0.7332202809505113</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7386601348322561</v>
+        <v>0.7386143700973495</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7482378497846353</v>
+        <v>0.7481961899620935</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7570050665686034</v>
+        <v>0.7569646400828265</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7730178462340402</v>
+        <v>0.773000124699571</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773563041261579</v>
+        <v>0.7773447334192998</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7779056381402855</v>
+        <v>0.777891635245932</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7833039716752885</v>
+        <v>0.7832961281561923</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885658631918435</v>
+        <v>0.7885639611879565</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923434630578499</v>
+        <v>0.7923441835403667</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893681270371788</v>
+        <v>0.7893627047274696</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920121246860002</v>
+        <v>0.7920032570317856</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7973835091502522</v>
+        <v>0.7973679691644842</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8024519024590122</v>
+        <v>0.8024312405493562</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8050867943482058</v>
+        <v>0.8050663453619735</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8076651660373082</v>
+        <v>0.8076472291097327</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098801071777035</v>
+        <v>0.8098657614465954</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096275378209661</v>
+        <v>0.8096237727537814</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.808893885868688</v>
+        <v>0.8089000095116157</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.809510341051649</v>
+        <v>0.8095161282513723</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8099742610460903</v>
+        <v>0.810034328764957</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8121802771923121</v>
+        <v>0.8121815430990078</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8160969311973278</v>
+        <v>0.8160356634275133</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8193965307344373</v>
+        <v>0.819301044174338</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8226679991925598</v>
+        <v>0.8226068706275138</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8262273268778231</v>
+        <v>0.8261541750954124</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8286855433798309</v>
+        <v>0.8286049075196807</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8278793910366493</v>
+        <v>0.8278465842378174</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8262781544508978</v>
+        <v>0.8262958694336815</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8240932639868541</v>
+        <v>0.8243616392826432</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8210200871718686</v>
+        <v>0.821532537005243</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8258932105816559</v>
+        <v>0.8263493808821625</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8298166353144366</v>
+        <v>0.8303771425936362</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8299856793546183</v>
+        <v>0.8323236365887132</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886301984463199</v>
+        <v>0.7886293726617368</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919410448884443</v>
+        <v>0.791939448274152</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.791303796193395</v>
+        <v>0.7913021778252797</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926789880346384</v>
+        <v>0.7926764236211655</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913527417255541</v>
+        <v>0.7913501021254026</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898999064495678</v>
+        <v>0.7898972266205255</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883224369246846</v>
+        <v>0.7883197704486762</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872401045237967</v>
+        <v>0.7872374871757716</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892470435660111</v>
+        <v>0.7892439686859151</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945043258150308</v>
+        <v>0.794502903230999</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969208671576313</v>
+        <v>0.7969193574109331</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993486555829262</v>
+        <v>0.7993471108960609</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001732883813559</v>
+        <v>0.8001725549090206</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986668324168549</v>
+        <v>0.7986673287096524</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992652817183521</v>
+        <v>0.7992662512930437</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039715715719302</v>
+        <v>0.8039710857309942</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096215524839154</v>
+        <v>0.8096195501060637</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157915775572777</v>
+        <v>0.8157888174599445</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221847615221956</v>
+        <v>0.8221825496743091</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229411570305769</v>
+        <v>0.8229406747775183</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187838612386735</v>
+        <v>0.8187860874922295</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153286581111019</v>
+        <v>0.8153317443339112</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139653974389293</v>
+        <v>0.8139711241294949</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123450646327078</v>
+        <v>0.8123542693173853</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8122108292653559</v>
+        <v>0.812222612113475</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8174234795329584</v>
+        <v>0.8174379612458117</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8231225298700944</v>
+        <v>0.8231387013227301</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8300056250521227</v>
+        <v>0.8300236025544108</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8346828892746601</v>
+        <v>0.834702740220602</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8198346491447922</v>
+        <v>0.8198574762145394</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8216569766852245</v>
+        <v>0.8216797444467543</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8091010732226556</v>
+        <v>0.8091259642118047</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.800984596496978</v>
+        <v>0.8010080645925122</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7937873303175251</v>
+        <v>0.7938143915875254</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7842075418148581</v>
+        <v>0.7842365743208962</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687003728413776</v>
+        <v>0.7687118017781605</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664649177089712</v>
+        <v>0.7664728662580717</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583452377540134</v>
+        <v>0.7583454799788406</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476636571420027</v>
+        <v>0.7476524102741173</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7387467984103071</v>
+        <v>0.7387288435456981</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7291449726650123</v>
+        <v>0.7291194525861606</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7332202809505113</v>
+        <v>0.7331781954618619</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7386143700973495</v>
+        <v>0.7385695264434805</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7481961899620935</v>
+        <v>0.748155358635777</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7569646400828265</v>
+        <v>0.7569250063650724</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.773000124699571</v>
+        <v>0.7729827492405</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773447334192998</v>
+        <v>0.7773333841701763</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.777891635245932</v>
+        <v>0.777877902584275</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832961281561923</v>
+        <v>0.7832884372481558</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885639611879565</v>
+        <v>0.7885621020374527</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923441835403667</v>
+        <v>0.7923449025793982</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893627047274696</v>
+        <v>0.7893573998761436</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7920032570317856</v>
+        <v>0.7919945768647991</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7973679691644842</v>
+        <v>0.7973527422749911</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8024312405493562</v>
+        <v>0.8024109864479838</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8050663453619735</v>
+        <v>0.8050462892678855</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8076472291097327</v>
+        <v>0.8076296179220208</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098657614465954</v>
+        <v>0.809851657141757</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096237727537814</v>
+        <v>0.8096200230801945</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089000095116157</v>
+        <v>0.8089059686474567</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095161282513723</v>
+        <v>0.8095217844344111</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.810034328764957</v>
+        <v>0.810187182950554</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8121815430990078</v>
+        <v>0.8123004968775527</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8160356634275133</v>
+        <v>0.8161302358447813</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.819301044174338</v>
+        <v>0.819403647053393</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8226068706275138</v>
+        <v>0.8227408470516411</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8261541750954124</v>
+        <v>0.8262979060045403</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8286049075196807</v>
+        <v>0.8287736331015056</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8278465842378174</v>
+        <v>0.8280963596618742</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8262958694336815</v>
+        <v>0.8266244512169274</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8243616392826432</v>
+        <v>0.8249901016665914</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.821532537005243</v>
+        <v>0.8224784983085418</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8263493808821625</v>
+        <v>0.8274199107649807</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8303771425936362</v>
+        <v>0.8319164048162853</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8323236365887132</v>
+        <v>0.8365738818824727</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886293726617368</v>
+        <v>0.7886285635579511</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791939448274152</v>
+        <v>0.7919378838534195</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913021778252797</v>
+        <v>0.7913005918924341</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926764236211655</v>
+        <v>0.7926739107585363</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913501021254026</v>
+        <v>0.7913475156008143</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898972266205255</v>
+        <v>0.789894600695025</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883197704486762</v>
+        <v>0.78831715761788</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872374871757716</v>
+        <v>0.7872349224845521</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892439686859151</v>
+        <v>0.7892409555464155</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794502903230999</v>
+        <v>0.794501509375225</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969193574109331</v>
+        <v>0.7969178781782288</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993471108960609</v>
+        <v>0.7993455974537578</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001725549090206</v>
+        <v>0.800171835899779</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986673287096524</v>
+        <v>0.7986678145177503</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992662512930437</v>
+        <v>0.7992672011284446</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039710857309942</v>
+        <v>0.803970609312329</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096195501060637</v>
+        <v>0.8096175871354253</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157888174599445</v>
+        <v>0.8157861104762563</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221825496743091</v>
+        <v>0.8221803797268772</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229406747775183</v>
+        <v>0.8229401992836797</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187860874922295</v>
+        <v>0.8187882649652717</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153317443339112</v>
+        <v>0.8153347642559641</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139711241294949</v>
+        <v>0.813976731477867</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123542693173853</v>
+        <v>0.8123632839862438</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.812222612113475</v>
+        <v>0.8122341532525803</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8174379612458117</v>
+        <v>0.8174521470913616</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8231387013227301</v>
+        <v>0.823154543746784</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8300236025544108</v>
+        <v>0.8300412154910513</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.834702740220602</v>
+        <v>0.8347221980160268</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8198574762145394</v>
+        <v>0.8198798453678138</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8216797444467543</v>
+        <v>0.8217020564612323</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8091259642118047</v>
+        <v>0.8091503551782095</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8010080645925122</v>
+        <v>0.8010310625376055</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7938143915875254</v>
+        <v>0.7938409130521979</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7842365743208962</v>
+        <v>0.7842650329255982</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687118017781605</v>
+        <v>0.7687230111855143</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664728662580717</v>
+        <v>0.7664806698458837</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583454799788406</v>
+        <v>0.7583457358196813</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476524102741173</v>
+        <v>0.7476414079943201</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7387288435456981</v>
+        <v>0.738711271249354</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7291194525861606</v>
+        <v>0.7290944632987938</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7331781954618619</v>
+        <v>0.7331369538126296</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7385695264434805</v>
+        <v>0.7385255763972294</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.748155358635777</v>
+        <v>0.748115331391682</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7569250063650724</v>
+        <v>0.7568861423879799</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7729827492405</v>
+        <v>0.7729657098455116</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773333841701763</v>
+        <v>0.7773222501086023</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.777877902584275</v>
+        <v>0.7778644324333205</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832884372481558</v>
+        <v>0.7832808945465539</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885621020374527</v>
+        <v>0.7885602843180863</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923449025793982</v>
+        <v>0.7923456198256633</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893573998761436</v>
+        <v>0.7893522087253646</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919945768647991</v>
+        <v>0.7919860783229251</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7973527422749911</v>
+        <v>0.7973378191560316</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8024109864479838</v>
+        <v>0.8023911282736367</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8050462892678855</v>
+        <v>0.8050266149633615</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8076296179220208</v>
+        <v>0.807612323859069</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.809851657141757</v>
+        <v>0.8098377884744687</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096200230801945</v>
+        <v>0.8096162900506153</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089059686474567</v>
+        <v>0.808911769177355</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095217844344111</v>
+        <v>0.8095273136646901</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.810187182950554</v>
+        <v>0.8103327594019818</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8123004968775527</v>
+        <v>0.8124142369776997</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8161302358447813</v>
+        <v>0.8162338845667729</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.819403647053393</v>
+        <v>0.8195530851282424</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8227408470516411</v>
+        <v>0.8229264691950366</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8262979060045403</v>
+        <v>0.8265191825051317</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8287736331015056</v>
+        <v>0.8290494388045169</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8280963596618742</v>
+        <v>0.8284807422155771</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8266244512169274</v>
+        <v>0.8271118319290435</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8249901016665914</v>
+        <v>0.8258311297207366</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8224784983085418</v>
+        <v>0.8236403286470075</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8274199107649807</v>
+        <v>0.828695478762894</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8319164048162853</v>
+        <v>0.833539685577473</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8365738818824727</v>
+        <v>0.8395317658513117</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886285635579511</v>
+        <v>0.7886277706346063</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919378838534195</v>
+        <v>0.7919363506623238</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7913005918924341</v>
+        <v>0.7912990374296008</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926739107585363</v>
+        <v>0.7926714479080245</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913475156008143</v>
+        <v>0.791344980567162</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789894600695025</v>
+        <v>0.7898920270631536</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.78831715761788</v>
+        <v>0.7883145968297933</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872349224845521</v>
+        <v>0.7872324088771608</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892409555464155</v>
+        <v>0.7892380023069245</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794501509375225</v>
+        <v>0.7945001433863289</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969178781782288</v>
+        <v>0.7969164285438364</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993455974537578</v>
+        <v>0.7993441143176875</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800171835899779</v>
+        <v>0.8001711309304538</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986678145177503</v>
+        <v>0.7986682901691169</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992672011284446</v>
+        <v>0.7992681318209696</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803970609312329</v>
+        <v>0.8039701420451899</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096175871354253</v>
+        <v>0.8096156624217175</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157861104762563</v>
+        <v>0.815783455092923</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221803797268772</v>
+        <v>0.8221782505065804</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229401992836797</v>
+        <v>0.8229397304350369</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187882649652717</v>
+        <v>0.818790395232105</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153347642559641</v>
+        <v>0.8153377199799376</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813976731477867</v>
+        <v>0.813982223166257</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123632839862438</v>
+        <v>0.8123721144501261</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8122341532525803</v>
+        <v>0.8122454600286668</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8174521470913616</v>
+        <v>0.8174660460250773</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.823154543746784</v>
+        <v>0.8231700670593438</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8300412154910513</v>
+        <v>0.830058474812943</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8347221980160268</v>
+        <v>0.8347412742115325</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8198798453678138</v>
+        <v>0.819901770233487</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8217020564612323</v>
+        <v>0.8217239262634606</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8091503551782095</v>
+        <v>0.8091742610198228</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8010310625376055</v>
+        <v>0.8010536043003145</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7938409130521979</v>
+        <v>0.793866910675133</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7842650329255982</v>
+        <v>0.7842929344378717</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687230111855143</v>
+        <v>0.7687340072986311</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664806698458837</v>
+        <v>0.7664883323472019</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583457358196813</v>
+        <v>0.7583460043185362</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476414079943201</v>
+        <v>0.7476306424635853</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.738711271249354</v>
+        <v>0.7386940694814823</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7290944632987938</v>
+        <v>0.7290699884564855</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7331369538126296</v>
+        <v>0.7330965309168911</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7385255763972294</v>
+        <v>0.738482493564796</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.748115331391682</v>
+        <v>0.7480760847634296</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7568861423879799</v>
+        <v>0.7568480260048409</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7729657098455116</v>
+        <v>0.7729489968846208</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773222501086023</v>
+        <v>0.7773113251977761</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7778644324333205</v>
+        <v>0.7778512173614829</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832808945465539</v>
+        <v>0.7832734958144028</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885602843180863</v>
+        <v>0.7885585066694807</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923456198256633</v>
+        <v>0.7923463349591918</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893522087253646</v>
+        <v>0.789347127675237</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919860783229251</v>
+        <v>0.79197775578509</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7973378191560316</v>
+        <v>0.7973231908469237</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8023911282736367</v>
+        <v>0.8023716545992189</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8050266149633615</v>
+        <v>0.8050073117556686</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.807612323859069</v>
+        <v>0.8075953385994532</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098377884744687</v>
+        <v>0.8098241498284902</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096162900506153</v>
+        <v>0.8096125748034542</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.808911769177355</v>
+        <v>0.8089174167410103</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095273136646901</v>
+        <v>0.8095327198506713</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8103327594019818</v>
+        <v>0.8105081821513631</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8124142369776997</v>
+        <v>0.812570174494214</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8162338845667729</v>
+        <v>0.8163991077657446</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8195530851282424</v>
+        <v>0.8197799677244906</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8229264691950366</v>
+        <v>0.8232028377221472</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8265191825051317</v>
+        <v>0.826843687407499</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8290494388045169</v>
+        <v>0.8294410795551623</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8284807422155771</v>
+        <v>0.828987085953778</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8271118319290435</v>
+        <v>0.827721898959826</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8258311297207366</v>
+        <v>0.8267938390336794</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8236403286470075</v>
+        <v>0.824934148914409</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.828695478762894</v>
+        <v>0.8301696838299801</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.833539685577473</v>
+        <v>0.8354750039745128</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8395317658513117</v>
+        <v>0.8400741135822427</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886277706346063</v>
+        <v>0.7886269934111594</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919363506623238</v>
+        <v>0.791934847775041</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912990374296008</v>
+        <v>0.7912975135094397</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926714479080245</v>
+        <v>0.7926690335915298</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791344980567162</v>
+        <v>0.7913424955022681</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898920270631536</v>
+        <v>0.7898895041784667</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883145968297933</v>
+        <v>0.7883120865451009</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872324088771608</v>
+        <v>0.7872299448426447</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892380023069245</v>
+        <v>0.7892351071992775</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7945001433863289</v>
+        <v>0.7944988044370216</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969164285438364</v>
+        <v>0.7969150076283424</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993441143176875</v>
+        <v>0.7993426605867151</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001711309304538</v>
+        <v>0.8001704395941993</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986682901691169</v>
+        <v>0.7986687559782137</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992681318209696</v>
+        <v>0.7992690439432584</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039701420451899</v>
+        <v>0.8039696836690767</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096156624217175</v>
+        <v>0.8096137748589273</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.815783455092923</v>
+        <v>0.8157808498533895</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221782505065804</v>
+        <v>0.8221761608832492</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229397304350369</v>
+        <v>0.8229392681185983</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818790395232105</v>
+        <v>0.8187924798004248</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153377199799376</v>
+        <v>0.8153406135209279</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.813982223166257</v>
+        <v>0.8139876027273025</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123721144501261</v>
+        <v>0.8123807662858158</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8122454600286668</v>
+        <v>0.8122565394936407</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8174660460250773</v>
+        <v>0.8174796666453676</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8231700670593438</v>
+        <v>0.8231852807838171</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.830058474812943</v>
+        <v>0.8300753910377832</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8347412742115325</v>
+        <v>0.8347599799102021</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.819901770233487</v>
+        <v>0.8199232639054127</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8217239262634606</v>
+        <v>0.8217453668580876</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8091742610198228</v>
+        <v>0.8091976960493279</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8010536043003145</v>
+        <v>0.8010757033015861</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.793866910675133</v>
+        <v>0.7938923997977321</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7842929344378717</v>
+        <v>0.7843202950181916</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687340072986311</v>
+        <v>0.7687447961200053</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664883323472019</v>
+        <v>0.7664958575023055</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583460043185362</v>
+        <v>0.7583462845768354</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476306424635853</v>
+        <v>0.7476201061723947</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7386940694814823</v>
+        <v>0.7386772267001008</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7290699884564855</v>
+        <v>0.7290460123755806</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7330965309168911</v>
+        <v>0.7330569026717033</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.738482493564796</v>
+        <v>0.7384402525795923</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7480760847634296</v>
+        <v>0.7480375961868431</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7568480260048409</v>
+        <v>0.7568106359080281</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7729489968846208</v>
+        <v>0.7729326010912445</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773113251977761</v>
+        <v>0.7773006036235752</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7778512173614829</v>
+        <v>0.7778382502141118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832734958144028</v>
+        <v>0.7832662369744698</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885585066694807</v>
+        <v>0.7885567677898182</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923463349591918</v>
+        <v>0.7923470476871328</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789347127675237</v>
+        <v>0.7893421532756248</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.79197775578509</v>
+        <v>0.7919696038590385</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7973231908469237</v>
+        <v>0.7973088487344366</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8023716545992189</v>
+        <v>0.8023525544304468</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8050073117556686</v>
+        <v>0.8049883693434134</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8075953385994532</v>
+        <v>0.8075786541034127</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098241498284902</v>
+        <v>0.8098107357543055</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096125748034542</v>
+        <v>0.8096088783733694</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089174167410103</v>
+        <v>0.8089229167303353</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095327198506713</v>
+        <v>0.8095380067522258</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105081821513631</v>
+        <v>0.8105109889023655</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.812570174494214</v>
+        <v>0.8127414331610561</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8163991077657446</v>
+        <v>0.8165471097507828</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8197799677244906</v>
+        <v>0.8198712251403663</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8232028377221472</v>
+        <v>0.8233321233123038</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.826843687407499</v>
+        <v>0.8269910584376854</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8294410795551623</v>
+        <v>0.8296212624564089</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.828987085953778</v>
+        <v>0.829259876512893</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.827721898959826</v>
+        <v>0.8280947807033808</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8267938390336794</v>
+        <v>0.8272959620707702</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.824934148914409</v>
+        <v>0.8258154691861643</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8301696838299801</v>
+        <v>0.8311856610625954</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8354750039745128</v>
+        <v>0.8368479026310416</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,15 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8400741135822427</v>
+        <v>0.8426624603870614</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B82">
+        <v>0.8565974603870613</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886269934111594</v>
+        <v>0.7886262314259083</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791934847775041</v>
+        <v>0.7919333743019822</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912975135094397</v>
+        <v>0.7912960192406863</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926690335915298</v>
+        <v>0.7926666663886219</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913424955022681</v>
+        <v>0.7913400589433589</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898895041784667</v>
+        <v>0.7898870305548912</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883120865451009</v>
+        <v>0.7883096252845924</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872299448426447</v>
+        <v>0.7872275289290477</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892351071992775</v>
+        <v>0.7892322685242066</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944988044370216</v>
+        <v>0.7944974917324337</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969150076283424</v>
+        <v>0.7969136145868254</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993426605867151</v>
+        <v>0.7993412353950751</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001704395941993</v>
+        <v>0.8001697614997236</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986687559782137</v>
+        <v>0.7986692122466805</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992690439432584</v>
+        <v>0.7992699380453474</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039696836690767</v>
+        <v>0.8039692339332565</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096137748589273</v>
+        <v>0.8096119233832051</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157808498533895</v>
+        <v>0.8157782933552101</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221761608832492</v>
+        <v>0.8221741097679097</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229392681185983</v>
+        <v>0.8229388122225219</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187924798004248</v>
+        <v>0.8187945201147834</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153406135209279</v>
+        <v>0.8153434468109442</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139876027273025</v>
+        <v>0.8139928735515694</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123807662858158</v>
+        <v>0.8123892448476825</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8122565394936407</v>
+        <v>0.8122673984198623</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8174796666453676</v>
+        <v>0.8174930172111643</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8231852807838171</v>
+        <v>0.823200194069231</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8300753910377832</v>
+        <v>0.8300919742712276</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8347599799102021</v>
+        <v>0.8347783257890418</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8199232639054127</v>
+        <v>0.819944338968399</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8217453668580876</v>
+        <v>0.8217663907452895</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8091976960493279</v>
+        <v>0.809220674022564</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8010757033015861</v>
+        <v>0.8010973724417484</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7938923997977321</v>
+        <v>0.7939173951691738</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7843202950181916</v>
+        <v>0.7843471302094868</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687447961200053</v>
+        <v>0.7687553834301299</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7664958575023055</v>
+        <v>0.7665032489226208</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583462845768354</v>
+        <v>0.758346575751489</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476201061723947</v>
+        <v>0.7476097919236904</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7386772267001008</v>
+        <v>0.7386607318356699</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7290460123755806</v>
+        <v>0.7290225200020193</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7330569026717033</v>
+        <v>0.7330180459095014</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7384402525795923</v>
+        <v>0.7383988290528538</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7480375961868431</v>
+        <v>0.7479998439571058</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7568106359080281</v>
+        <v>0.7567739515897502</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7729326010912445</v>
+        <v>0.7729165135452709</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7773006036235752</v>
+        <v>0.7772900797844358</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7778382502141118</v>
+        <v>0.7778255241007574</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832662369744698</v>
+        <v>0.7832591141018265</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885567677898182</v>
+        <v>0.7885550664327393</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923470476871328</v>
+        <v>0.7923477577417359</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893421532756248</v>
+        <v>0.7893372822184743</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919696038590385</v>
+        <v>0.7919616173698429</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7973088487344366</v>
+        <v>0.7972947845361873</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8023525544304468</v>
+        <v>0.8023338171856818</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8049883693434134</v>
+        <v>0.8049697777990154</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8075786541034127</v>
+        <v>0.8075622626013967</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8098107357543055</v>
+        <v>0.8097975409635579</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096088783733694</v>
+        <v>0.8096052016988935</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089229167303353</v>
+        <v>0.8089282743022982</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095380067522258</v>
+        <v>0.8095431779871742</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105109889023655</v>
+        <v>0.8105137432521353</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8127414331610561</v>
+        <v>0.8129199166678195</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8165471097507828</v>
+        <v>0.8167054219309594</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8198712251403663</v>
+        <v>0.8199837467939844</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8233321233123038</v>
+        <v>0.8234945759137084</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8269910584376854</v>
+        <v>0.8271767063703725</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8296212624564089</v>
+        <v>0.8298518366417957</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.829259876512893</v>
+        <v>0.8295919117541173</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8280947807033808</v>
+        <v>0.8285329929642198</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8272959620707702</v>
+        <v>0.8278703200499936</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8258154691861643</v>
+        <v>0.8267734399964214</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8311856610625954</v>
+        <v>0.8322886005470431</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8368479026310416</v>
+        <v>0.8382952317060179</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8426624603870614</v>
+        <v>0.8450802246032204</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8565974603870613</v>
+        <v>0.8590152246032203</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8129199166678195</v>
+        <v>0.8130842783751198</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8167054219309594</v>
+        <v>0.816916452341406</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8199837467939844</v>
+        <v>0.8202340256263703</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8234945759137084</v>
+        <v>0.8237779769142339</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8271767063703725</v>
+        <v>0.8274865369534692</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8298518366417957</v>
+        <v>0.8301992873808615</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8295919117541173</v>
+        <v>0.8299814568990005</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8285329929642198</v>
+        <v>0.8289600217264235</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8278703200499936</v>
+        <v>0.8283633110060248</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8267734399964214</v>
+        <v>0.8273947790374371</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8322886005470431</v>
+        <v>0.8330753693486468</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8382952317060179</v>
+        <v>0.839377423990175</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8450802246032204</v>
+        <v>0.8470407407205817</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8590152246032203</v>
+        <v>0.8612738657205816</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886262314259083</v>
+        <v>0.7886254842350793</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919333743019822</v>
+        <v>0.7919319293880375</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912960192406863</v>
+        <v>0.7912945537664126</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926666663886219</v>
+        <v>0.7926643449337544</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913400589433589</v>
+        <v>0.7913376694841943</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898870305548912</v>
+        <v>0.7898846047638077</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883096252845924</v>
+        <v>0.7883072116262566</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872275289290477</v>
+        <v>0.7872251597405594</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892322685242066</v>
+        <v>0.7892294846480181</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944974917324337</v>
+        <v>0.7944962045085444</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969136145868254</v>
+        <v>0.79691224860718</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993412353950751</v>
+        <v>0.7993398379106541</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001697614997236</v>
+        <v>0.8001690962705515</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986692122466805</v>
+        <v>0.7986696592639823</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992699380453474</v>
+        <v>0.7992708146557734</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039692339332565</v>
+        <v>0.8039687925963102</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096119233832051</v>
+        <v>0.8096101069708768</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157782933552101</v>
+        <v>0.8157757842475697</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221741097679097</v>
+        <v>0.8221720961109362</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229388122225219</v>
+        <v>0.8229383626362181</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187945201147834</v>
+        <v>0.8187965175598458</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153434468109442</v>
+        <v>0.8153462217031314</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139928735515694</v>
+        <v>0.8139980388946065</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123892448476825</v>
+        <v>0.8123975552786395</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8122673984198623</v>
+        <v>0.8122780433138355</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8174930172111643</v>
+        <v>0.8175061056584796</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.823200194069231</v>
+        <v>0.8232148157084107</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8300919742712276</v>
+        <v>0.8301082342268282</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8347783257890418</v>
+        <v>0.8347963221191984</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.819944338968399</v>
+        <v>0.8199650075226854</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8217663907452895</v>
+        <v>0.8217870099449717</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.809220674022564</v>
+        <v>0.8092432081653124</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8010973724417484</v>
+        <v>0.8011186241254766</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7939173951691738</v>
+        <v>0.7939419109746657</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7843471302094868</v>
+        <v>0.7843734549662866</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687553834301299</v>
+        <v>0.7687657747976056</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665032489226208</v>
+        <v>0.7665105100961025</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758346575751489</v>
+        <v>0.7583468770512243</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7476097919236904</v>
+        <v>0.7475996928168719</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7386607318356699</v>
+        <v>0.7386445742672556</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7290225200020193</v>
+        <v>0.7289994968801277</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7330180459095014</v>
+        <v>0.7329799383532322</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7383988290528538</v>
+        <v>0.7383581995270657</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7479998439571058</v>
+        <v>0.7479628071883323</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7567739515897502</v>
+        <v>0.7567379533049836</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7729165135452709</v>
+        <v>0.7729007256570652</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772900797844358</v>
+        <v>0.7772797482817737</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7778255241007574</v>
+        <v>0.7778130323831309</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832591141018265</v>
+        <v>0.7832521234168113</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885550664327393</v>
+        <v>0.7885534014044356</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923477577417359</v>
+        <v>0.79234846487849</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893372822184743</v>
+        <v>0.7893325113305989</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919616173698429</v>
+        <v>0.7919537913490966</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7972947845361873</v>
+        <v>0.7972809902849757</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8023338171856818</v>
+        <v>0.8023154326768753</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8049697777990154</v>
+        <v>0.8049515275520993</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8075622626013967</v>
+        <v>0.8075461565831412</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097975409635579</v>
+        <v>0.8097845603236615</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8096052016988935</v>
+        <v>0.809601545629489</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089282743022982</v>
+        <v>0.808933494391006</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095431779871742</v>
+        <v>0.8095482370375098</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105137432521353</v>
+        <v>0.8105164464258043</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8130842783751198</v>
+        <v>0.8134329146543676</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.816916452341406</v>
+        <v>0.8172958716195768</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8202340256263703</v>
+        <v>0.8206131259109534</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8237779769142339</v>
+        <v>0.8242411916888959</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8274865369534692</v>
+        <v>0.8280003852506013</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8301992873808615</v>
+        <v>0.8307959739997983</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8299814568990005</v>
+        <v>0.8307183342969982</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8289600217264235</v>
+        <v>0.8298359181020452</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8283633110060248</v>
+        <v>0.829431814316007</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8273947790374371</v>
+        <v>0.8289436989775797</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8330753693486468</v>
+        <v>0.8348995808854621</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.839377423990175</v>
+        <v>0.8417376467034668</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8470407407205817</v>
+        <v>0.8507057457641461</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8612738657205816</v>
+        <v>0.8745000501094602</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886254842350793</v>
+        <v>0.788624751411963</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919319293880375</v>
+        <v>0.791930512210923</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912945537664126</v>
+        <v>0.7912931162623915</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926643449337544</v>
+        <v>0.7926620679136402</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913376694841943</v>
+        <v>0.7913353257723633</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898846047638077</v>
+        <v>0.789882225431302</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883072116262566</v>
+        <v>0.7883048442025438</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872251597405594</v>
+        <v>0.7872228359348271</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892294846480181</v>
+        <v>0.7892267539994602</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944962045085444</v>
+        <v>0.7944949420306977</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.79691224860718</v>
+        <v>0.7969109089085396</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993398379106541</v>
+        <v>0.7993384673333703</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001690962705515</v>
+        <v>0.800168443544331</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986696592639823</v>
+        <v>0.7986700973080156</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992708146557734</v>
+        <v>0.7992716742826131</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039687925963102</v>
+        <v>0.8039683594257061</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096101069708768</v>
+        <v>0.8096083246365693</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157757842475697</v>
+        <v>0.8157733212289395</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221720961109362</v>
+        <v>0.8221701189003012</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229383626362181</v>
+        <v>0.8229379192504374</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187965175598458</v>
+        <v>0.8187984734634437</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153462217031314</v>
+        <v>0.8153489399757379</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8139980388946065</v>
+        <v>0.8140031018835863</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8123975552786395</v>
+        <v>0.8124057025204603</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8122780433138355</v>
+        <v>0.812288480429102</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8175061056584796</v>
+        <v>0.817518939616005</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8232148157084107</v>
+        <v>0.8232291541551128</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8301082342268282</v>
+        <v>0.8301241802448247</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8347963221191984</v>
+        <v>0.8348139787850404</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8199650075226854</v>
+        <v>0.8199852812070214</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8217870099449717</v>
+        <v>0.8218072360195932</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8092432081653124</v>
+        <v>0.8092653111985535</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8011186241254766</v>
+        <v>0.8011394702853397</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7939419109746657</v>
+        <v>0.7939659608621011</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7843734549662866</v>
+        <v>0.7843992836822349</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687657747976056</v>
+        <v>0.7687759755887119</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665105100961025</v>
+        <v>0.7665176443923603</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583468770512243</v>
+        <v>0.7583471877331917</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475996928168719</v>
+        <v>0.7475898022327628</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7386445742672556</v>
+        <v>0.7386287438001163</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7289994968801277</v>
+        <v>0.7289769291232429</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7329799383532322</v>
+        <v>0.7329425585740403</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7383581995270657</v>
+        <v>0.738318341432022</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7479628071883323</v>
+        <v>0.7479264657753939</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7567379533049836</v>
+        <v>0.7567026220364347</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7729007256570652</v>
+        <v>0.7728852291523487</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772797482817737</v>
+        <v>0.7772696039109165</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7778130323831309</v>
+        <v>0.7778007686637118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832521234168113</v>
+        <v>0.78324526127838</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885534014044356</v>
+        <v>0.7885517715609243</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.79234846487849</v>
+        <v>0.7923491688744027</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893325113305989</v>
+        <v>0.7893278375669018</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919537913490966</v>
+        <v>0.7919461210247443</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7972809902849757</v>
+        <v>0.7972674583139963</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8023154326768753</v>
+        <v>0.8022973910915504</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8049515275520993</v>
+        <v>0.8049336093737558</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8075461565831412</v>
+        <v>0.8075303287872501</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097845603236615</v>
+        <v>0.8097717888525944</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.809601545629489</v>
+        <v>0.8095979109320772</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.808933494391006</v>
+        <v>0.8089385817190745</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095482370375098</v>
+        <v>0.809553187255323</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105164464258043</v>
+        <v>0.8105190996201639</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8134329146543676</v>
+        <v>0.813766079036197</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8172958716195768</v>
+        <v>0.8176075278380177</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8206131259109534</v>
+        <v>0.8208028788695145</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8242411916888959</v>
+        <v>0.8242701851841677</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8280003852506013</v>
+        <v>0.8279494535121867</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8307959739997983</v>
+        <v>0.8306714819541405</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8307183342969982</v>
+        <v>0.8306720240195393</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8298359181020452</v>
+        <v>0.829965104110685</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.829431814316007</v>
+        <v>0.8297506593573714</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8289436989775797</v>
+        <v>0.8294670837083824</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8348995808854621</v>
+        <v>0.8352583896459124</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8417376467034668</v>
+        <v>0.8416941249919944</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8507057457641461</v>
+        <v>0.8495722912321524</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8745000501094602</v>
+        <v>0.86564091418595</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788624751411963</v>
+        <v>0.788624032546104</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791930512210923</v>
+        <v>0.7919291219796197</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912931162623915</v>
+        <v>0.7912917059355509</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926620679136402</v>
+        <v>0.7926598340647765</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913353257723633</v>
+        <v>0.7913330265067345</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789882225431302</v>
+        <v>0.7898798912355711</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883048442025438</v>
+        <v>0.7883025216977841</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872228359348271</v>
+        <v>0.787220556220422</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892267539994602</v>
+        <v>0.7892240750667692</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944949420306977</v>
+        <v>0.7944937035922077</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969109089085396</v>
+        <v>0.7969095947397901</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993384673333703</v>
+        <v>0.7993371228936492</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800168443544331</v>
+        <v>0.8001678029721785</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986700973080156</v>
+        <v>0.7986705266456804</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992716742826131</v>
+        <v>0.7992725174144647</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039683594257061</v>
+        <v>0.8039679341973958</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096083246365693</v>
+        <v>0.8096065754314373</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157733212289395</v>
+        <v>0.815770903044857</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221701189003012</v>
+        <v>0.8221681771599172</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229379192504374</v>
+        <v>0.8229374819573425</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8187984734634437</v>
+        <v>0.8188003890994491</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153489399757379</v>
+        <v>0.8153516033358472</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140031018835863</v>
+        <v>0.8140080655235571</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124057025204603</v>
+        <v>0.8124136913234992</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.812288480429102</v>
+        <v>0.8122987157783951</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.817518939616005</v>
+        <v>0.8175315264198175</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8232291541551128</v>
+        <v>0.8232432175401776</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8301241802448247</v>
+        <v>0.8301398213098692</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8348139787850404</v>
+        <v>0.8348313053021719</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8199852812070214</v>
+        <v>0.820005171220441</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8218072360195932</v>
+        <v>0.821827080095703</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8092653111985535</v>
+        <v>0.8092869953622948</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8011394702853397</v>
+        <v>0.8011599224040187</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7939659608621011</v>
+        <v>0.7939895579672173</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7843992836822349</v>
+        <v>0.7844246302160771</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687759755887119</v>
+        <v>0.7687859909764625</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665176443923603</v>
+        <v>0.7665246550675344</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583471877331917</v>
+        <v>0.758347507099812</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475898022327628</v>
+        <v>0.7475801138194772</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7386287438001163</v>
+        <v>0.7386132306446166</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7289769291232429</v>
+        <v>0.7289548033860505</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7329425585740403</v>
+        <v>0.732905885951342</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.738318341432022</v>
+        <v>0.7382792330433433</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7479264657753939</v>
+        <v>0.747890800357857</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7567026220364347</v>
+        <v>0.7566679394614177</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7728852291523487</v>
+        <v>0.772870016057898</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772696039109165</v>
+        <v>0.7772596416525156</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7778007686637118</v>
+        <v>0.7777887267749704</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.78324526127838</v>
+        <v>0.783238524177818</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885517715609243</v>
+        <v>0.7885501758054873</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923491688744027</v>
+        <v>0.7923498695264148</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893278375669018</v>
+        <v>0.7893232580039994</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919461210247443</v>
+        <v>0.7919386018115057</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7972674583139963</v>
+        <v>0.7972541812428732</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8022973910915504</v>
+        <v>0.8022796829757595</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8049336093737558</v>
+        <v>0.8049160143616136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8075303287872501</v>
+        <v>0.8075147721912563</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097717888525944</v>
+        <v>0.8097592217138643</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095979109320772</v>
+        <v>0.8095942982970828</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089385817190745</v>
+        <v>0.8089435408083376</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.809553187255323</v>
+        <v>0.8095580318684397</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105190996201639</v>
+        <v>0.8105217040038513</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.813766079036197</v>
+        <v>0.8139903552621948</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8176075278380177</v>
+        <v>0.8177820943434866</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8208028788695145</v>
+        <v>0.8208742513684868</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8242701851841677</v>
+        <v>0.8242111986537519</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8279494535121867</v>
+        <v>0.8277678523200734</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8306714819541405</v>
+        <v>0.8304235039172756</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8306720240195393</v>
+        <v>0.8304990499193252</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.829965104110685</v>
+        <v>0.8299543558690218</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8297506593573714</v>
+        <v>0.8298997368999206</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8294670837083824</v>
+        <v>0.8297800041125936</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8352583896459124</v>
+        <v>0.8353723328518788</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8416941249919944</v>
+        <v>0.8413792554787731</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8495722912321524</v>
+        <v>0.848216997796426</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.86564091418595</v>
+        <v>0.8594167687892451</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788624032546104</v>
+        <v>0.7886233272425331</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919291219796197</v>
+        <v>0.7919277579329023</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912917059355509</v>
+        <v>0.7912903220225154</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926598340647765</v>
+        <v>0.7926576421711066</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913330265067345</v>
+        <v>0.791330770435047</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898798912355711</v>
+        <v>0.7898776009044759</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883025216977841</v>
+        <v>0.7883002428457505</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.787220556220422</v>
+        <v>0.7872183193544473</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892240750667692</v>
+        <v>0.7892214463948797</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944937035922077</v>
+        <v>0.794492488513038</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969095947397901</v>
+        <v>0.796908305378165</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993371228936492</v>
+        <v>0.7993358038509815</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001678029721785</v>
+        <v>0.8001671742180587</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986705266456804</v>
+        <v>0.7986709475334168</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992725174144647</v>
+        <v>0.7992733445213702</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039679341973958</v>
+        <v>0.8039675166954314</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096065754314373</v>
+        <v>0.8096048584414892</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.815770903044857</v>
+        <v>0.8157685284858259</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221681771599172</v>
+        <v>0.8221662699480637</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229374819573425</v>
+        <v>0.8229370506505718</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188003890994491</v>
+        <v>0.8188022656904728</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153516033358472</v>
+        <v>0.8153542134228879</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140080655235571</v>
+        <v>0.8140129327033352</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124136913234992</v>
+        <v>0.8124215262558543</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8122987157783951</v>
+        <v>0.8123087551450983</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8175315264198175</v>
+        <v>0.8175438731272497</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8232432175401776</v>
+        <v>0.8232570136867716</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8301398213098692</v>
+        <v>0.8301551660677511</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8348313053021719</v>
+        <v>0.834848310834451</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.820005171220441</v>
+        <v>0.8200246883428146</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.821827080095703</v>
+        <v>0.8218465528842716</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8092869953622948</v>
+        <v>0.809308272438063</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8011599224040187</v>
+        <v>0.8011799915352829</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7939895579672173</v>
+        <v>0.7940127149373564</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7844246302160771</v>
+        <v>0.7844495079162218</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687859909764625</v>
+        <v>0.7687958259491853</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665246550675344</v>
+        <v>0.7665315452689427</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758347507099812</v>
+        <v>0.7583478344958542</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475801138194772</v>
+        <v>0.747570621479128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7386132306446166</v>
+        <v>0.7385980253963742</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7289548033860505</v>
+        <v>0.728933106838514</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.732905885951342</v>
+        <v>0.7328699006351295</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7382792330433433</v>
+        <v>0.7382408534432972</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.747890800357857</v>
+        <v>0.7478557922858948</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7566679394614177</v>
+        <v>0.7566338879205129</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.772870016057898</v>
+        <v>0.7728550786880155</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772596416525156</v>
+        <v>0.7772498566644077</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777887267749704</v>
+        <v>0.7777769007691553</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.783238524177818</v>
+        <v>0.7832319087327893</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885501758054873</v>
+        <v>0.788548613086268</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923498695264148</v>
+        <v>0.7923505666499331</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893232580039994</v>
+        <v>0.7893187698342208</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919386018115057</v>
+        <v>0.7919312293018524</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7972541812428732</v>
+        <v>0.7972411519644618</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8022796829757595</v>
+        <v>0.8022622992179541</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8049160143616136</v>
+        <v>0.8048987339256808</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8075147721912563</v>
+        <v>0.8074994800021378</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097592217138643</v>
+        <v>0.8097468542116475</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095942982970828</v>
+        <v>0.8095907083440337</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089435408083376</v>
+        <v>0.8089483759899335</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095580318684397</v>
+        <v>0.8095627739857899</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105217040038513</v>
+        <v>0.810524260717602</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8139903552621948</v>
+        <v>0.8139918970466815</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8177820943434866</v>
+        <v>0.8178224430783165</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8208742513684868</v>
+        <v>0.8208602381290911</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8242111986537519</v>
+        <v>0.8240775881397161</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8277678523200734</v>
+        <v>0.8275801068549002</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8304235039172756</v>
+        <v>0.8302208279257617</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8304990499193252</v>
+        <v>0.8303908931352406</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8299543558690218</v>
+        <v>0.8299450328722475</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8298997368999206</v>
+        <v>0.8299144126055026</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8297800041125936</v>
+        <v>0.8297604732052977</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8353723328518788</v>
+        <v>0.8350404493183343</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8413792554787731</v>
+        <v>0.8405503536323539</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.848216997796426</v>
+        <v>0.8464478907423321</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,15 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8594167687892451</v>
+        <v>0.8544836173930483</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B83">
+        <v>0.8431136173930485</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886233272425331</v>
+        <v>0.7886226351210441</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919277579329023</v>
+        <v>0.7919264193379489</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912903220225154</v>
+        <v>0.7912889637882299</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926576421711066</v>
+        <v>0.7926554910618151</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791330770435047</v>
+        <v>0.7913285563516383</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898776009044759</v>
+        <v>0.7898753532132313</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7883002428457505</v>
+        <v>0.7882980064273576</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872183193544473</v>
+        <v>0.7872161241402795</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892214463948797</v>
+        <v>0.7892188665827946</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794492488513038</v>
+        <v>0.794491296138559</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.796908305378165</v>
+        <v>0.7969070401279216</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993358038509815</v>
+        <v>0.799334509492565</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001671742180587</v>
+        <v>0.8001665569581987</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986709475334168</v>
+        <v>0.798671360217712</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992733445213702</v>
+        <v>0.7992741560556887</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039675166954314</v>
+        <v>0.8039671067116041</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096048584414892</v>
+        <v>0.8096031727860032</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157685284858259</v>
+        <v>0.8157661963853267</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221662699480637</v>
+        <v>0.8221643963558986</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229370506505718</v>
+        <v>0.8229366252252897</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188022656904728</v>
+        <v>0.8188041044104051</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153542134228879</v>
+        <v>0.8153567718119424</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140129327033352</v>
+        <v>0.8140177062010576</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124215262558543</v>
+        <v>0.8124292117120093</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123087551450983</v>
+        <v>0.8123186040940591</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8175438731272497</v>
+        <v>0.81755598652998</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8232570136867716</v>
+        <v>0.8232705501247761</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8301551660677511</v>
+        <v>0.8301702228411914</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.834848310834451</v>
+        <v>0.8348650042100749</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8200246883428146</v>
+        <v>0.8200438429542634</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8218465528842716</v>
+        <v>0.8218656646998963</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.809308272438063</v>
+        <v>0.809329153770148</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8011799915352829</v>
+        <v>0.8011996883238055</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7940127149373564</v>
+        <v>0.7940354439539192</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7844495079162218</v>
+        <v>0.7844739296439622</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7687958259491853</v>
+        <v>0.7688054853186486</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665315452689427</v>
+        <v>0.7665383180395038</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583478344958542</v>
+        <v>0.7583481693057149</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.747570621479128</v>
+        <v>0.7475613193553161</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7385980253963742</v>
+        <v>0.7385831190175624</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.728933106838514</v>
+        <v>0.7289118271412953</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7328699006351295</v>
+        <v>0.7328345835103607</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7382408534432972</v>
+        <v>0.7382031824837703</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7478557922858948</v>
+        <v>0.7478214235880509</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7566338879205129</v>
+        <v>0.7566004503879069</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7728550786880155</v>
+        <v>0.7728404096317179</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772498566644077</v>
+        <v>0.7772402442738999</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777769007691553</v>
+        <v>0.7777652849086252</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832319087327893</v>
+        <v>0.7832254116817055</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788548613086268</v>
+        <v>0.7885470823940129</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923505666499331</v>
+        <v>0.7923512600774744</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893187698342208</v>
+        <v>0.7893143703599597</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919312293018524</v>
+        <v>0.7919239992575018</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7972411519644618</v>
+        <v>0.7972283636323723</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8022622992179541</v>
+        <v>0.8022452310337143</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048987339256808</v>
+        <v>0.8048817597749049</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074994800021378</v>
+        <v>0.8074844456472658</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097468542116475</v>
+        <v>0.8097346817860906</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095907083440337</v>
+        <v>0.8095871416267475</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089483759899335</v>
+        <v>0.8089530914138114</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095627739857899</v>
+        <v>0.8095674166025173</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.810524260717602</v>
+        <v>0.8105267708745594</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8139918970466815</v>
+        <v>0.8139934472404796</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8178224430783165</v>
+        <v>0.817962951208612</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8208602381290911</v>
+        <v>0.8209630248874056</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8240775881397161</v>
+        <v>0.8240763852036457</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8275801068549002</v>
+        <v>0.8275693242330764</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8302208279257617</v>
+        <v>0.8302240331512747</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8303908931352406</v>
+        <v>0.8304933727550069</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8299450328722475</v>
+        <v>0.8301335072792224</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8299144126055026</v>
+        <v>0.830123637688065</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8297604732052977</v>
+        <v>0.8299476983961613</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8350404493183343</v>
+        <v>0.834963480186195</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8405503536323539</v>
+        <v>0.8401044824076334</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8464478907423321</v>
+        <v>0.845415070313948</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8544836173930483</v>
+        <v>0.851808215405634</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8431136173930485</v>
+        <v>0.8404382154056341</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886226351210441</v>
+        <v>0.7886219558155108</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919264193379489</v>
+        <v>0.7919251054890293</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912889637882299</v>
+        <v>0.7912876305246589</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926554910618151</v>
+        <v>0.7926533796092434</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913285563516383</v>
+        <v>0.7913263830952978</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898753532132313</v>
+        <v>0.7898731469822233</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882980064273576</v>
+        <v>0.788295811268489</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872161241402795</v>
+        <v>0.7872139694254352</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892188665827946</v>
+        <v>0.7892163342810945</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794491296138559</v>
+        <v>0.7944901258383716</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969070401279216</v>
+        <v>0.7969057983190893</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799334509492565</v>
+        <v>0.7993332391320207</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001665569581987</v>
+        <v>0.8001659508805357</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.798671360217712</v>
+        <v>0.7986717649355779</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992741560556887</v>
+        <v>0.7992749524529197</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039671067116041</v>
+        <v>0.8039667040451016</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096031727860032</v>
+        <v>0.8096015176160304</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157661963853267</v>
+        <v>0.8157639056179299</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221643963558986</v>
+        <v>0.8221625555060419</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229366252252897</v>
+        <v>0.8229362055782286</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188041044104051</v>
+        <v>0.8188059063868066</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153567718119424</v>
+        <v>0.8153592800168596</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140177062010576</v>
+        <v>0.8140223886894239</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124292117120093</v>
+        <v>0.8124367519209901</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123186040940591</v>
+        <v>0.8123282679817958</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.81755598652998</v>
+        <v>0.8175678731663933</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8232705501247761</v>
+        <v>0.8232838341043752</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8301702228411914</v>
+        <v>0.8301849996447603</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8348650042100749</v>
+        <v>0.8348813939367932</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8200438429542634</v>
+        <v>0.8200626450535013</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8218656646998963</v>
+        <v>0.8218844254789526</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.809329153770148</v>
+        <v>0.809349650285677</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8011996883238055</v>
+        <v>0.8012190230238927</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7940354439539192</v>
+        <v>0.794057756753592</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7844739296439622</v>
+        <v>0.7844979077954463</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688054853186486</v>
+        <v>0.7688149737277674</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665383180395038</v>
+        <v>0.7665449763219522</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583481693057149</v>
+        <v>0.758348510950894</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475613193553161</v>
+        <v>0.7475522018213483</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7385831190175624</v>
+        <v>0.7385685028192842</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7289118271412953</v>
+        <v>0.7288909524225661</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7328345835103607</v>
+        <v>0.7327999161633061</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7382031824837703</v>
+        <v>0.7381662007512604</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7478214235880509</v>
+        <v>0.7477876769407401</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7566004503879069</v>
+        <v>0.7565676104433027</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7728404096317179</v>
+        <v>0.7728260017406037</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772402442738999</v>
+        <v>0.7772307999704511</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777652849086252</v>
+        <v>0.7777538736566793</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832254116817055</v>
+        <v>0.7832190298783913</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885470823940129</v>
+        <v>0.7885455827599445</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923512600774744</v>
+        <v>0.7923519496574132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893143703599597</v>
+        <v>0.78931005698835</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919239992575018</v>
+        <v>0.7919169076013926</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7972283636323723</v>
+        <v>0.7972158096491662</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8022452310337143</v>
+        <v>0.8022284699512816</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048817597749049</v>
+        <v>0.8048650839044161</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074844456472658</v>
+        <v>0.8074696627657638</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097346817860906</v>
+        <v>0.8097227000087794</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095871416267475</v>
+        <v>0.8095835986381419</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089530914138114</v>
+        <v>0.8089576910576965</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095674166025173</v>
+        <v>0.8095719626048468</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105267708745594</v>
+        <v>0.8105292355606316</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8139934472404796</v>
+        <v>0.8139950045088876</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.817962951208612</v>
+        <v>0.818227987558966</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8209630248874056</v>
+        <v>0.8212176021026096</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8240763852036457</v>
+        <v>0.8242801593037262</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8275693242330764</v>
+        <v>0.8278059371349877</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8302240331512747</v>
+        <v>0.83051938195214</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8304933727550069</v>
+        <v>0.8308983729920437</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8301335072792224</v>
+        <v>0.8306244874961561</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.830123637688065</v>
+        <v>0.8306583590209913</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8299476983961613</v>
+        <v>0.8305147477936652</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.834963480186195</v>
+        <v>0.8354098006027935</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8401044824076334</v>
+        <v>0.8404043966283906</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.845415070313948</v>
+        <v>0.8456200840597567</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.851808215405634</v>
+        <v>0.8517485351266983</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8404382154056341</v>
+        <v>0.8430221923110448</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886219558155108</v>
+        <v>0.7886212889732402</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919251054890293</v>
+        <v>0.7919238157062639</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912876305246589</v>
+        <v>0.7912863215495559</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926533796092434</v>
+        <v>0.7926513067269196</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913263830952978</v>
+        <v>0.791324249547236</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898731469822233</v>
+        <v>0.7898709810749458</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.788295811268489</v>
+        <v>0.7882936562379429</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872139694254352</v>
+        <v>0.7872118540995553</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892163342810945</v>
+        <v>0.7892138481895877</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944901258383716</v>
+        <v>0.7944889770051969</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969057983190893</v>
+        <v>0.796904579306288</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993332391320207</v>
+        <v>0.7993319921081801</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001659508805357</v>
+        <v>0.8001653556841914</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986717649355779</v>
+        <v>0.7986721619149998</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992749524529197</v>
+        <v>0.7992757341324804</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039667040451016</v>
+        <v>0.8039663085021832</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8096015176160304</v>
+        <v>0.8095998921129743</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157639056179299</v>
+        <v>0.8157616550975109</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221625555060419</v>
+        <v>0.8221607465512344</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229362055782286</v>
+        <v>0.8229357916077223</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188059063868066</v>
+        <v>0.8188076727031619</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153592800168596</v>
+        <v>0.8153617394931922</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140223886894239</v>
+        <v>0.8140269827406393</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124367519209901</v>
+        <v>0.8124441509540656</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123282679817958</v>
+        <v>0.8123377519661407</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8175678731663933</v>
+        <v>0.81757953933326</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8232838341043752</v>
+        <v>0.8232968726088989</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8301849996447603</v>
+        <v>0.8301995041989804</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8348813939367932</v>
+        <v>0.8348974882162991</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8200626450535013</v>
+        <v>0.820081104275181</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8218844254789526</v>
+        <v>0.821902844796757</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.809349650285677</v>
+        <v>0.809369772513594</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8012190230238927</v>
+        <v>0.8012380055171928</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.794057756753592</v>
+        <v>0.7940796646484254</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7844979077954463</v>
+        <v>0.7845214543224687</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688149737277674</v>
+        <v>0.7688242956579086</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665449763219522</v>
+        <v>0.7665515229628563</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758348510950894</v>
+        <v>0.7583488588876451</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475522018213483</v>
+        <v>0.7475432634691369</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7385685028192842</v>
+        <v>0.7385541684449533</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7288909524225661</v>
+        <v>0.7288704712561178</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7327999161633061</v>
+        <v>0.7327658808497214</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7381662007512604</v>
+        <v>0.7381298895337556</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7477876769407401</v>
+        <v>0.7477545356393726</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7565676104433027</v>
+        <v>0.7565353522453079</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7728260017406037</v>
+        <v>0.7728118481173556</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772307999704511</v>
+        <v>0.7772215193987291</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777538736566793</v>
+        <v>0.777742661668865</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832190298783913</v>
+        <v>0.7832127602870309</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885455827599445</v>
+        <v>0.7885441132537636</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923519496574132</v>
+        <v>0.792352635252821</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.78931005698835</v>
+        <v>0.7893058272262494</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919169076013926</v>
+        <v>0.7919099504101131</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7972158096491662</v>
+        <v>0.797203483655186</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8022284699512816</v>
+        <v>0.8022120077978481</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048650839044161</v>
+        <v>0.8048486985834062</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074696627657638</v>
+        <v>0.8074551252002568</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097227000087794</v>
+        <v>0.8097109045783597</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095835986381419</v>
+        <v>0.8095800798146916</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089576910576965</v>
+        <v>0.808962178735544</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095719626048468</v>
+        <v>0.809576414774718</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105292355606316</v>
+        <v>0.8105316558348867</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8139950045088876</v>
+        <v>0.8139965676072249</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.818227987558966</v>
+        <v>0.8184816988294962</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8212176021026096</v>
+        <v>0.821448777379582</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8242801593037262</v>
+        <v>0.8244612558967369</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8278059371349877</v>
+        <v>0.8280167330832688</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.83051938195214</v>
+        <v>0.8307933851981589</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8308983729920437</v>
+        <v>0.8312746906990631</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8306244874961561</v>
+        <v>0.831076044653614</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8306583590209913</v>
+        <v>0.8311364183842358</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8305147477936652</v>
+        <v>0.8310006750385086</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8354098006027935</v>
+        <v>0.8357536568029393</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8404043966283906</v>
+        <v>0.8405792093615114</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8456200840597567</v>
+        <v>0.8456544571345265</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8517485351266983</v>
+        <v>0.8514689857975501</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8430221923110448</v>
+        <v>0.8455964247670581</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8184816988294962</v>
+        <v>0.8184991782838204</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.821448777379582</v>
+        <v>0.8214733290860818</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8244612558967369</v>
+        <v>0.8244955035397044</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8280167330832688</v>
+        <v>0.8280804270678923</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8307933851981589</v>
+        <v>0.8308828505835679</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8312746906990631</v>
+        <v>0.8313959962658812</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.831076044653614</v>
+        <v>0.831221614554277</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8311364183842358</v>
+        <v>0.8313041657847655</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8310006750385086</v>
+        <v>0.8311942657841651</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8357536568029393</v>
+        <v>0.8360271674488762</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8405792093615114</v>
+        <v>0.8409601989697523</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8456544571345265</v>
+        <v>0.8462881899017307</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8514689857975501</v>
+        <v>0.852667585408813</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8455964247670581</v>
+        <v>0.8486043877336734</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886212889732402</v>
+        <v>0.7886206342543632</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919238157062639</v>
+        <v>0.7919225493344517</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912863215495559</v>
+        <v>0.7912850362053001</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926513067269196</v>
+        <v>0.7926492713676951</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791324249547236</v>
+        <v>0.7913221546291659</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898709810749458</v>
+        <v>0.7898688543960493</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882936562379429</v>
+        <v>0.7882915402454895</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872118540995553</v>
+        <v>0.7872097770924973</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892138481895877</v>
+        <v>0.7892114070550863</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944889770051969</v>
+        <v>0.7944878490538261</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.796904579306288</v>
+        <v>0.7969033824676099</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993319921081801</v>
+        <v>0.7993307677839376</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001653556841914</v>
+        <v>0.800164771078977</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986721619149998</v>
+        <v>0.7986725513753636</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992757341324804</v>
+        <v>0.7992765014984419</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039663085021832</v>
+        <v>0.8039659198958719</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095998921129743</v>
+        <v>0.8095982954872507</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157616550975109</v>
+        <v>0.8157594437755529</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221607465512344</v>
+        <v>0.8221589686730626</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229357916077223</v>
+        <v>0.8229353832137322</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188076727031619</v>
+        <v>0.818809404401</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153617394931922</v>
+        <v>0.8153641516409654</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140269827406393</v>
+        <v>0.8140314908310853</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124441509540656</v>
+        <v>0.8124514127320241</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123377519661407</v>
+        <v>0.81234706101535</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.81757953933326</v>
+        <v>0.8175909910967744</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8232968726088989</v>
+        <v>0.8233096723669662</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8301995041989804</v>
+        <v>0.8302137439436622</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8348974882162991</v>
+        <v>0.8349132949578555</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.820081104275181</v>
+        <v>0.8200992299062995</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.821902844796757</v>
+        <v>0.8219209318838061</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.809369772513594</v>
+        <v>0.8093895306026146</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8012380055171928</v>
+        <v>0.8012566453294527</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7940796646484254</v>
+        <v>0.7941011785448384</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7845214543224687</v>
+        <v>0.7845445807521627</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688242956579086</v>
+        <v>0.7688334554358253</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665515229628563</v>
+        <v>0.7665579607164483</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583488588876451</v>
+        <v>0.7583492126047882</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475432634691369</v>
+        <v>0.7475344990987333</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7385541684449533</v>
+        <v>0.7385401078546117</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7288704712561178</v>
+        <v>0.7288503726406905</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7327658808497214</v>
+        <v>0.7327324604647386</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7381298895337556</v>
+        <v>0.7380942307893896</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7477545356393726</v>
+        <v>0.7477219835710099</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7565353522453079</v>
+        <v>0.756503660506211</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7728118481173556</v>
+        <v>0.7727979421048401</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772215193987291</v>
+        <v>0.7772123983520198</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.777742661668865</v>
+        <v>0.7777316437847314</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832127602870309</v>
+        <v>0.7832065999773777</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885441132537636</v>
+        <v>0.7885426729817666</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.792352635252821</v>
+        <v>0.7923533167403936</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893058272262494</v>
+        <v>0.7893016786755055</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7919099504101131</v>
+        <v>0.79190312390675</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.797203483655186</v>
+        <v>0.7971913795179804</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8022120077978481</v>
+        <v>0.802195836686559</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048486985834062</v>
+        <v>0.8048325963436158</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074551252002568</v>
+        <v>0.8074408269889894</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8097109045783597</v>
+        <v>0.8096992913163155</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095800798146916</v>
+        <v>0.8095765855405653</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.808962178735544</v>
+        <v>0.8089665581055201</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.809576414774718</v>
+        <v>0.8095807757942006</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105316558348867</v>
+        <v>0.8105340327299857</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8139965676072249</v>
+        <v>0.8139981353749233</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8184991782838204</v>
+        <v>0.8187589550075061</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8214733290860818</v>
+        <v>0.8217181397894917</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8244955035397044</v>
+        <v>0.8247015639599773</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8280804270678923</v>
+        <v>0.8283429222673908</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8308828505835679</v>
+        <v>0.8312296176729919</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8313959962658812</v>
+        <v>0.8318694419023012</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.831221614554277</v>
+        <v>0.8317883618447408</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8313041657847655</v>
+        <v>0.831913940969236</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8311942657841651</v>
+        <v>0.8318311097271326</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8360271674488762</v>
+        <v>0.8365989941870797</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8409601989697523</v>
+        <v>0.8414654892277332</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8462881899017307</v>
+        <v>0.8468709267997216</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.852667585408813</v>
+        <v>0.85340126563035</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8486043877336734</v>
+        <v>0.8519507919668148</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886206342543632</v>
+        <v>0.7886199913312567</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919225493344517</v>
+        <v>0.7919213057419603</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912850362053001</v>
+        <v>0.7912837738577955</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926492713676951</v>
+        <v>0.7926472725219821</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913221546291659</v>
+        <v>0.7913200973014868</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898688543960493</v>
+        <v>0.789866765889495</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882915402454895</v>
+        <v>0.7882894622400325</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872097770924973</v>
+        <v>0.7872077373725316</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892114070550863</v>
+        <v>0.7892090096693013</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944878490538261</v>
+        <v>0.7944867414201271</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969033824676099</v>
+        <v>0.7969022072035623</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993307677839376</v>
+        <v>0.7993295655451673</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800164771078977</v>
+        <v>0.8001641967849217</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986725513753636</v>
+        <v>0.7986729335278553</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992765014984419</v>
+        <v>0.7992772549402239</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039659198958719</v>
+        <v>0.803965538045663</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095982954872507</v>
+        <v>0.8095967269770141</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157594437755529</v>
+        <v>0.81575727063954</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221589686730626</v>
+        <v>0.822157221080749</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229353832137322</v>
+        <v>0.8229349802978656</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818809404401</v>
+        <v>0.818811102481898</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153641516409654</v>
+        <v>0.8153665178072915</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140314908310853</v>
+        <v>0.8140359153457326</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124514127320241</v>
+        <v>0.8124585410320493</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.81234706101535</v>
+        <v>0.812356199916723</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8175909910967744</v>
+        <v>0.8176022343029945</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233096723669662</v>
+        <v>0.8233222398639697</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8302137439436622</v>
+        <v>0.830227726050522</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349132949578555</v>
+        <v>0.8349288217911988</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8200992299062995</v>
+        <v>0.8201170309017275</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219209318838061</v>
+        <v>0.8219386956411465</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8093895306026146</v>
+        <v>0.8094089343382171</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8012566453294527</v>
+        <v>0.8012749516463787</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941011785448384</v>
+        <v>0.7941223089616093</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7845445807521627</v>
+        <v>0.7845672982056532</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688334554358253</v>
+        <v>0.7688424572402363</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665579607164483</v>
+        <v>0.7665642922482763</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583492126047882</v>
+        <v>0.7583495716216728</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475344990987333</v>
+        <v>0.7475259037084542</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7385401078546117</v>
+        <v>0.7385263133101233</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7288503726406905</v>
+        <v>0.728830645980437</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7327324604647386</v>
+        <v>0.7326996385143627</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7380942307893896</v>
+        <v>0.7380592071167559</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7477219835710099</v>
+        <v>0.7476900051884512</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.756503660506211</v>
+        <v>0.75647252046806</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727979421048401</v>
+        <v>0.7727842772757691</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772123983520198</v>
+        <v>0.7772034327659664</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777316437847314</v>
+        <v>0.7777208150200009</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832065999773777</v>
+        <v>0.7832005461202092</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885426729817666</v>
+        <v>0.7885412610850713</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923533167403936</v>
+        <v>0.7923539940094557</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893016786755055</v>
+        <v>0.7892976090284893</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.79190312390675</v>
+        <v>0.7918964244541313</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971913795179804</v>
+        <v>0.7971794913222838</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.802195836686559</v>
+        <v>0.8021799490041799</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048325963436158</v>
+        <v>0.8048167699683882</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074408269889894</v>
+        <v>0.8074267623582994</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096992913163155</v>
+        <v>0.8096878561628937</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095765855405653</v>
+        <v>0.8095731161514625</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089665581055201</v>
+        <v>0.8089708326775347</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095807757942006</v>
+        <v>0.8095850482496987</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105340327299857</v>
+        <v>0.810536367252638</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8139981353749233</v>
+        <v>0.8139997067300289</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8187589550075061</v>
+        <v>0.8190116214684207</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8217181397894917</v>
+        <v>0.8219531057600498</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8247015639599773</v>
+        <v>0.8248855033635702</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8283429222673908</v>
+        <v>0.8285490530738566</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8312296176729919</v>
+        <v>0.8314978502659256</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8318694419023012</v>
+        <v>0.8322359532412118</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8317883618447408</v>
+        <v>0.832236782892344</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.831913940969236</v>
+        <v>0.8324104984094693</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8318311097271326</v>
+        <v>0.832369313929658</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8365989941870797</v>
+        <v>0.8370764906583179</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8414654892277332</v>
+        <v>0.84186595990945</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8468709267997216</v>
+        <v>0.8472625110926104</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.85340126563035</v>
+        <v>0.8537363593818978</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8519507919668148</v>
+        <v>0.8535600195562238</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886199913312567</v>
+        <v>0.7886193598879965</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919213057419603</v>
+        <v>0.791920084319675</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912837738577955</v>
+        <v>0.7912825338954282</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926472725219821</v>
+        <v>0.7926453092160846</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913200973014868</v>
+        <v>0.7913180765615643</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789866765889495</v>
+        <v>0.7898647145368076</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882894622400325</v>
+        <v>0.7882874212078691</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872077373725316</v>
+        <v>0.7872057339446332</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892090096693013</v>
+        <v>0.7892066548668497</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944867414201271</v>
+        <v>0.7944856535601038</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969022072035623</v>
+        <v>0.7969010529360669</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993295655451673</v>
+        <v>0.799328384799695</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001641967849217</v>
+        <v>0.8001636325318287</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986729335278553</v>
+        <v>0.7986733085758393</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992772549402239</v>
+        <v>0.7992779948332529</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803965538045663</v>
+        <v>0.8039651627772464</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095967269770141</v>
+        <v>0.8095951858469526</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.81575727063954</v>
+        <v>0.8157551347114289</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.822157221080749</v>
+        <v>0.8221555030099996</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229349802978656</v>
+        <v>0.8229345827633898</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818811102481898</v>
+        <v>0.8188127679093694</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153665178072915</v>
+        <v>0.8153688392888367</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140359153457326</v>
+        <v>0.8140402585823121</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124585410320493</v>
+        <v>0.8124655394942266</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.812356199916723</v>
+        <v>0.8123651732847503</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176022343029945</v>
+        <v>0.8176132745877227</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233222398639697</v>
+        <v>0.8233345813529502</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.830227726050522</v>
+        <v>0.8302414574351271</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349288217911988</v>
+        <v>0.8349440760787669</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8201170309017275</v>
+        <v>0.8201345158989124</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219386956411465</v>
+        <v>0.8219561446549299</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8094089343382171</v>
+        <v>0.809427993158734</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8012749516463787</v>
+        <v>0.801292933328658</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941223089616093</v>
+        <v>0.7941430660469234</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7845672982056532</v>
+        <v>0.7845896174157405</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688424572402363</v>
+        <v>0.7688513051080761</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665642922482763</v>
+        <v>0.7665705201386888</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583495716216728</v>
+        <v>0.7583499354862837</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475259037084542</v>
+        <v>0.7475174724855642</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7385263133101233</v>
+        <v>0.738512777361191</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.728830645980437</v>
+        <v>0.7288112810664542</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7326996385143627</v>
+        <v>0.7326673990884809</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7380592071167559</v>
+        <v>0.7380248017267883</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7476900051884512</v>
+        <v>0.7476585854856687</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.75647252046806</v>
+        <v>0.7564419178799696</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727842772757691</v>
+        <v>0.7727708474228887</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772034327659664</v>
+        <v>0.7771946187126222</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777208150200009</v>
+        <v>0.7777101705591376</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832005461202092</v>
+        <v>0.7831945959830159</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885412610850713</v>
+        <v>0.7885398767379455</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923539940094557</v>
+        <v>0.7923546669610417</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892976090284893</v>
+        <v>0.7892936160638779</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918964244541313</v>
+        <v>0.7918898485484406</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971794913222838</v>
+        <v>0.7971678133605216</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8021799490041799</v>
+        <v>0.8021643373993965</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048167699683882</v>
+        <v>0.8048012124822617</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8074267623582994</v>
+        <v>0.807412925715423</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096878561628937</v>
+        <v>0.8096765951731734</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095731161514625</v>
+        <v>0.8095696719381758</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089708326775347</v>
+        <v>0.8089750058203574</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095850482496987</v>
+        <v>0.8095892346359583</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.810536367252638</v>
+        <v>0.8105386603840823</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8139997067300289</v>
+        <v>0.8140012806640855</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190116214684207</v>
+        <v>0.8190132950359087</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8219531057600498</v>
+        <v>0.822235022311669</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8248855033635702</v>
+        <v>0.8251690541963093</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8285490530738566</v>
+        <v>0.8288244767977346</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8314978502659256</v>
+        <v>0.8317923183022621</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8322359532412118</v>
+        <v>0.8326553979673614</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.832236782892344</v>
+        <v>0.8327714581152468</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8324104984094693</v>
+        <v>0.8330476948796159</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.832369313929658</v>
+        <v>0.8331203937667959</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8370764906583179</v>
+        <v>0.8378026435200443</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.84186595990945</v>
+        <v>0.8427109564439872</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8472625110926104</v>
+        <v>0.8482706134957425</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8537363593818978</v>
+        <v>0.8549586302226487</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,15 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8535600195562238</v>
+        <v>0.8562737087958374</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B84">
+        <v>0.8676437087958373</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886193598879965</v>
+        <v>0.7886187396198399</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791920084319675</v>
+        <v>0.7919188844800054</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912825338954282</v>
+        <v>0.7912813157280801</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926453092160846</v>
+        <v>0.7926433805106173</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913180765615643</v>
+        <v>0.7913160914421031</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898647145368076</v>
+        <v>0.7898626993554198</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882874212078691</v>
+        <v>0.7882854161710433</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872057339446332</v>
+        <v>0.7872037658488644</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892066548668497</v>
+        <v>0.7892043415233675</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944856535601038</v>
+        <v>0.794484584949006</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969010529360669</v>
+        <v>0.7968999191075119</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799328384799695</v>
+        <v>0.7993272249763262</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001636325318287</v>
+        <v>0.8001630780588519</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986733085758393</v>
+        <v>0.7986736767152184</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992779948332529</v>
+        <v>0.7992787215395836</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039651627772464</v>
+        <v>0.8039647939222445</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095951858469526</v>
+        <v>0.8095936713871419</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157551347114289</v>
+        <v>0.8157530350461994</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221555030099996</v>
+        <v>0.822153813721911</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229345827633898</v>
+        <v>0.8229341905152396</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188127679093694</v>
+        <v>0.8188144016106462</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153688392888367</v>
+        <v>0.8153711173341518</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140402585823121</v>
+        <v>0.8140445227552594</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124655394942266</v>
+        <v>0.8124724116276957</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123651732847503</v>
+        <v>0.8123739855688303</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176132745877227</v>
+        <v>0.8176241173858574</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233345813529502</v>
+        <v>0.8233467028648888</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8302414574351271</v>
+        <v>0.8302549447682088</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349440760787669</v>
+        <v>0.8349590649272918</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8201345158989124</v>
+        <v>0.8201516932318094</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219561446549299</v>
+        <v>0.8219732872102072</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.809427993158734</v>
+        <v>0.8094467161705936</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.801292933328658</v>
+        <v>0.8013105989261904</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941430660469234</v>
+        <v>0.7941634595945255</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7845896174157405</v>
+        <v>0.7846115487436682</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688513051080761</v>
+        <v>0.7688600029404311</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665705201386888</v>
+        <v>0.7665766468861583</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583499354862837</v>
+        <v>0.7583503037734698</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475174724855642</v>
+        <v>0.7475092007974757</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.738512777361191</v>
+        <v>0.7384994928321393</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7288112810664542</v>
+        <v>0.7287922680593135</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7326673990884809</v>
+        <v>0.7326357268352841</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7380248017267883</v>
+        <v>0.7379909984161028</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7476585854856687</v>
+        <v>0.7476277099745089</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7564419178799696</v>
+        <v>0.7564118389765802</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727708474228887</v>
+        <v>0.7727576465496652</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771946187126222</v>
+        <v>0.7771859523947982</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777101705591376</v>
+        <v>0.7776997057482857</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831945959830159</v>
+        <v>0.7831887469259095</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885398767379455</v>
+        <v>0.7885385191462296</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923546669610417</v>
+        <v>0.7923553355070398</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892936160638779</v>
+        <v>0.789289697642669</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918898485484406</v>
+        <v>0.7918833928131759</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971678133605216</v>
+        <v>0.7971563401238073</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8021643373993965</v>
+        <v>0.8021489947717042</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8048012124822617</v>
+        <v>0.8047859171410673</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.807412925715423</v>
+        <v>0.8073993116416198</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096765951731734</v>
+        <v>0.8096655045132735</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095696719381758</v>
+        <v>0.8095662531498957</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089750058203574</v>
+        <v>0.8089790807683415</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095892346359583</v>
+        <v>0.8095933373598846</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105386603840823</v>
+        <v>0.8105409130805838</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140012806640855</v>
+        <v>0.8140028562373692</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190132950359087</v>
+        <v>0.8190150042179949</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.822235022311669</v>
+        <v>0.8225492142699398</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8251690541963093</v>
+        <v>0.8255024011989358</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8288244767977346</v>
+        <v>0.8291699832282292</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8317923183022621</v>
+        <v>0.8322109630410661</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8326553979673614</v>
+        <v>0.8332324718643699</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8327714581152468</v>
+        <v>0.8334780292754975</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8330476948796159</v>
+        <v>0.8338448487666421</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8331203937667959</v>
+        <v>0.8339893735601376</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8378026435200443</v>
+        <v>0.838595410454663</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8427109564439872</v>
+        <v>0.8435542129081821</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8482706134957425</v>
+        <v>0.849209253177802</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8549586302226487</v>
+        <v>0.8560140643450207</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8562737087958374</v>
+        <v>0.8583184008622746</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8676437087958373</v>
+        <v>0.8696884008622745</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8225492142699398</v>
+        <v>0.8225531949876823</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8255024011989358</v>
+        <v>0.8255073579790564</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8291699832282292</v>
+        <v>0.8291702786603923</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8322109630410661</v>
+        <v>0.8322618970197773</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8332324718643699</v>
+        <v>0.8332716486788451</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8334780292754975</v>
+        <v>0.8335118824575904</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8338448487666421</v>
+        <v>0.8338773367558674</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8339893735601376</v>
+        <v>0.8340234079786184</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.838595410454663</v>
+        <v>0.8386340437315019</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8435542129081821</v>
+        <v>0.8436044514752483</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.849209253177802</v>
+        <v>0.8492763197441168</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8560140643450207</v>
+        <v>0.8561122915816541</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8583184008622746</v>
+        <v>0.8584791624246705</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8696884008622745</v>
+        <v>0.8698491624246704</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886187396198399</v>
+        <v>0.788618130232736</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919188844800054</v>
+        <v>0.7919177056559423</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912813157280801</v>
+        <v>0.7912801187861906</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926433805106173</v>
+        <v>0.7926414854990083</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913160914421031</v>
+        <v>0.7913141410096025</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898626993554198</v>
+        <v>0.789860719397103</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882854161710433</v>
+        <v>0.7882834461857817</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872037658488644</v>
+        <v>0.7872018321588415</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892043415233675</v>
+        <v>0.7892020685537214</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.794484584949006</v>
+        <v>0.7944835350804863</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968999191075119</v>
+        <v>0.7968988051798551</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993272249763262</v>
+        <v>0.7993260855239268</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001630780588519</v>
+        <v>0.800162533114096</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986736767152184</v>
+        <v>0.7986740381347712</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992787215395836</v>
+        <v>0.7992794354084907</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039647939222445</v>
+        <v>0.8039644313179624</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095936713871419</v>
+        <v>0.8095921829119637</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157530350461994</v>
+        <v>0.8157509707304769</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.822153813721911</v>
+        <v>0.8221521525019301</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229341905152396</v>
+        <v>0.8229338034600207</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188144016106462</v>
+        <v>0.8188160044783641</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153711173341518</v>
+        <v>0.8153733531458784</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140445227552594</v>
+        <v>0.8140487099994488</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124724116276957</v>
+        <v>0.8124791608164776</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123739855688303</v>
+        <v>0.8123826410605754</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176241173858574</v>
+        <v>0.8176347679402511</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233467028648888</v>
+        <v>0.8233586102184611</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8302549447682088</v>
+        <v>0.8302681944863823</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349590649272918</v>
+        <v>0.8349737951987921</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8201516932318094</v>
+        <v>0.8201685709440848</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219732872102072</v>
+        <v>0.8219901313039997</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8094467161705936</v>
+        <v>0.8094651121627678</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8013105989261904</v>
+        <v>0.8013279566915819</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941634595945255</v>
+        <v>0.7941834990590391</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7846115487436682</v>
+        <v>0.7846331021950301</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688600029404311</v>
+        <v>0.7688685545081815</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665766468861583</v>
+        <v>0.7665826749104553</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583503037734698</v>
+        <v>0.7583506760832961</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475092007974757</v>
+        <v>0.7475010841834335</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7384994928321393</v>
+        <v>0.738486452809417</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7287922680593135</v>
+        <v>0.7287735974725265</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7326357268352841</v>
+        <v>0.7326046069370236</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7379909984161028</v>
+        <v>0.7379577815417213</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7476277099745089</v>
+        <v>0.7475973646625862</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7564118389765802</v>
+        <v>0.7563822704576029</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727576465496652</v>
+        <v>0.7727446688614408</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771859523947982</v>
+        <v>0.7771774301406864</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776997057482857</v>
+        <v>0.7776894160885605</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831887469259095</v>
+        <v>0.7831829963977346</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885385191462296</v>
+        <v>0.7885371875458493</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923553355070398</v>
+        <v>0.7923559995694035</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789289697642669</v>
+        <v>0.7892858517044147</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918833928131759</v>
+        <v>0.791877053993434</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971563401238073</v>
+        <v>0.7971450662934005</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8021489947717042</v>
+        <v>0.8021339142608568</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8047859171410673</v>
+        <v>0.8047708774225073</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073993116416198</v>
+        <v>0.8073859148856</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096655045132735</v>
+        <v>0.8096545804566972</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095662531498957</v>
+        <v>0.8095628599972849</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089790807683415</v>
+        <v>0.8089830606277784</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095933373598846</v>
+        <v>0.8095973587441834</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105409130805838</v>
+        <v>0.8105431262739469</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140028562373692</v>
+        <v>0.8140044325744495</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190150042179949</v>
+        <v>0.8190167464901661</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8225531949876823</v>
+        <v>0.8226503783814104</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8255073579790564</v>
+        <v>0.8255614545911394</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8291702786603923</v>
+        <v>0.8291759574160774</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8322618970197773</v>
+        <v>0.8322746398031744</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8332716486788451</v>
+        <v>0.8333133447916798</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8335118824575904</v>
+        <v>0.8336147582109299</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8338773367558674</v>
+        <v>0.8340282475503497</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8340234079786184</v>
+        <v>0.8342224996929785</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8386340437315019</v>
+        <v>0.8387207809318417</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8436044514752483</v>
+        <v>0.8435960598897787</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8492763197441168</v>
+        <v>0.8490462686803157</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8561122915816541</v>
+        <v>0.8553933511585877</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8584791624246705</v>
+        <v>0.8574081906732711</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8698491624246704</v>
+        <v>0.8689557290167536</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788618130232736</v>
+        <v>0.7886175314428605</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919177056559423</v>
+        <v>0.791916547300165</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912801187861906</v>
+        <v>0.791278942519872</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926414854990083</v>
+        <v>0.7926396233060788</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913141410096025</v>
+        <v>0.7913122243628948</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789860719397103</v>
+        <v>0.7898587737464819</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882834461857817</v>
+        <v>0.7882815103410158</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872018321588415</v>
+        <v>0.787199931980282</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892020685537214</v>
+        <v>0.7891998349103124</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944835350804863</v>
+        <v>0.7944825034657998</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968988051798551</v>
+        <v>0.7968977106337718</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993260855239268</v>
+        <v>0.7993249659105479</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800162533114096</v>
+        <v>0.8001619974542347</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986740381347712</v>
+        <v>0.7986743930164723</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992794354084907</v>
+        <v>0.799280136777026</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039644313179624</v>
+        <v>0.8039640748071499</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095921829119637</v>
+        <v>0.8095907197590728</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157509707304769</v>
+        <v>0.8157489408812216</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221521525019301</v>
+        <v>0.8221505186588631</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229338034600207</v>
+        <v>0.8229334215060087</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188160044783641</v>
+        <v>0.8188175773721529</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153733531458784</v>
+        <v>0.8153755478828302</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140487099994488</v>
+        <v>0.8140528223737293</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124791608164776</v>
+        <v>0.8124857903249945</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123826410605754</v>
+        <v>0.8123911439007331</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176347679402511</v>
+        <v>0.8176452313101066</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233586102184611</v>
+        <v>0.8233703090292825</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8302681944863823</v>
+        <v>0.8302812128023094</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349737951987921</v>
+        <v>0.834988273521009</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8201685709440848</v>
+        <v>0.8201851568016368</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219901313039997</v>
+        <v>0.8220066846576993</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8094651121627678</v>
+        <v>0.8094831896204746</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8013279566915819</v>
+        <v>0.8013450145929404</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941834990590391</v>
+        <v>0.7942031935704983</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7846331021950301</v>
+        <v>0.784654287434872</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688685545081815</v>
+        <v>0.7688769634573666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665826749104553</v>
+        <v>0.7665886065556767</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583506760832961</v>
+        <v>0.7583510520395051</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475010841834335</v>
+        <v>0.747493118346656</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.738486452809417</v>
+        <v>0.7384736506297745</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7287735974725265</v>
+        <v>0.7287552601568896</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7326046069370236</v>
+        <v>0.7325740250870162</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7379577815417213</v>
+        <v>0.7379251359970889</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7475973646625862</v>
+        <v>0.7475675360322931</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7563822704576029</v>
+        <v>0.7563531994683892</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727446688614408</v>
+        <v>0.7727319087570264</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771774301406864</v>
+        <v>0.7771690483987479</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776894160885605</v>
+        <v>0.7776792972296679</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831829963977346</v>
+        <v>0.7831773419323769</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885371875458493</v>
+        <v>0.78853588120141</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923559995694035</v>
+        <v>0.7923566590794139</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892858517044147</v>
+        <v>0.789282076263659</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.791877053993434</v>
+        <v>0.7918708289504992</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971450662934005</v>
+        <v>0.7971339867326025</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8021339142608568</v>
+        <v>0.8021190892368398</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8047708774225073</v>
+        <v>0.8047560870171856</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073859148856</v>
+        <v>0.8073727303572389</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096545804566972</v>
+        <v>0.8096438193808042</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095628599972849</v>
+        <v>0.8095594926553294</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089830606277784</v>
+        <v>0.80898694838291</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8095973587441834</v>
+        <v>0.8096013010308287</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105431262739469</v>
+        <v>0.8105453008720345</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140044325744495</v>
+        <v>0.8140060088600514</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190167464901661</v>
+        <v>0.8190185194648411</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8226503783814104</v>
+        <v>0.8227437176729531</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8255614545911394</v>
+        <v>0.8256129606607941</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8291759574160774</v>
+        <v>0.8291830814903089</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8322746398031744</v>
+        <v>0.8322905374276346</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8333133447916798</v>
+        <v>0.8333551297920927</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8336147582109299</v>
+        <v>0.8337147618760284</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8340282475503497</v>
+        <v>0.8341736231645454</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8342224996929785</v>
+        <v>0.8344129136753796</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8387207809318417</v>
+        <v>0.8388048641524479</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8435960598897787</v>
+        <v>0.8435917827538418</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8490462686803157</v>
+        <v>0.8488433959003251</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8553933511585877</v>
+        <v>0.8547782430233677</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8574081906732711</v>
+        <v>0.856562466123135</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8689557290167536</v>
+        <v>0.8648683780609425</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886175314428605</v>
+        <v>0.7886169429761742</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791916547300165</v>
+        <v>0.7919154088841931</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.791278942519872</v>
+        <v>0.7912777863980647</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926396233060788</v>
+        <v>0.7926377930866955</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913122243628948</v>
+        <v>0.7913103406317563</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898587737464819</v>
+        <v>0.7898568615196229</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882815103410158</v>
+        <v>0.7882796077569751</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.787199931980282</v>
+        <v>0.7871980644496259</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7891998349103124</v>
+        <v>0.7891976395814675</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944825034657998</v>
+        <v>0.7944814896330464</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968977106337718</v>
+        <v>0.7968966349678492</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993249659105479</v>
+        <v>0.7993238656226007</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001619974542347</v>
+        <v>0.8001614708441507</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986743930164723</v>
+        <v>0.798674741535796</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.799280136777026</v>
+        <v>0.7992808259705498</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039640748071499</v>
+        <v>0.8039637242377772</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095907197590728</v>
+        <v>0.8095892812884206</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157489408812216</v>
+        <v>0.8157469446444846</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221505186588631</v>
+        <v>0.8221489115239337</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229334215060087</v>
+        <v>0.8229330445631449</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188175773721529</v>
+        <v>0.8188191211201425</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153755478828302</v>
+        <v>0.8153777026619662</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140528223737293</v>
+        <v>0.8140568618642712</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124857903249945</v>
+        <v>0.8124923033032959</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123911439007331</v>
+        <v>0.8123994980857486</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176452313101066</v>
+        <v>0.8176555123789344</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233703090292825</v>
+        <v>0.8233818047186732</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8302812128023094</v>
+        <v>0.830294005714336</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.834988273521009</v>
+        <v>0.8350025062973072</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8201851568016368</v>
+        <v>0.820201458304475</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8220066846576993</v>
+        <v>0.822022954728834</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8094831896204746</v>
+        <v>0.8095009567381725</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8013450145929404</v>
+        <v>0.801361780326017</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7942031935704983</v>
+        <v>0.7942225519481403</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.784654287434872</v>
+        <v>0.7846751138020283</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688769634573666</v>
+        <v>0.7688852333142875</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665886065556767</v>
+        <v>0.7665944440931393</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583510520395051</v>
+        <v>0.7583514312880794</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.747493118346656</v>
+        <v>0.7474852991468997</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7384736506297745</v>
+        <v>0.7384610798690733</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7287552601568896</v>
+        <v>0.7287372472856536</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7325740250870162</v>
+        <v>0.7325439674678274</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7379251359970889</v>
+        <v>0.7378930471893117</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7475675360322931</v>
+        <v>0.7475382110208726</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7563531994683892</v>
+        <v>0.7563246135814632</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727319087570264</v>
+        <v>0.7727193608207139</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771690483987479</v>
+        <v>0.7771608037328452</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776792972296679</v>
+        <v>0.777669344963837</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831773419323769</v>
+        <v>0.7831717811452523</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.78853588120141</v>
+        <v>0.78853459940487</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923566590794139</v>
+        <v>0.7923573139770019</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.789282076263659</v>
+        <v>0.7892783694065669</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918708289504992</v>
+        <v>0.7918647146567173</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971339867326025</v>
+        <v>0.7971230964790603</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8021190892368398</v>
+        <v>0.8021045132903396</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8047560870171856</v>
+        <v>0.8047415398200637</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073727303572389</v>
+        <v>0.8073597531215655</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096438193808042</v>
+        <v>0.8096332177634098</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095594926553294</v>
+        <v>0.8095561512659892</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.80898694838291</v>
+        <v>0.8089907469016138</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096013010308287</v>
+        <v>0.8096051663843729</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105453008720345</v>
+        <v>0.8105474377592972</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140060088600514</v>
+        <v>0.8140075843351995</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190185194648411</v>
+        <v>0.8190203208836666</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8227437176729531</v>
+        <v>0.8228893099760829</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8256129606607941</v>
+        <v>0.8257313135115877</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8291830814903089</v>
+        <v>0.8292904022591261</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8322905374276346</v>
+        <v>0.8324365965340015</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8333551297920927</v>
+        <v>0.8335677698962605</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8337147618760284</v>
+        <v>0.8340051005029304</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8341736231645454</v>
+        <v>0.8345230481614975</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8344129136753796</v>
+        <v>0.8348179353603471</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8388048641524479</v>
+        <v>0.8391348196694381</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8435917827538418</v>
+        <v>0.8439195608437738</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8488433959003251</v>
+        <v>0.8491271513477077</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8547782430233677</v>
+        <v>0.8549513368143051</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.856562466123135</v>
+        <v>0.8569986620486203</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8648683780609425</v>
+        <v>0.8650103673233832</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886169429761742</v>
+        <v>0.7886163645680067</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919154088841931</v>
+        <v>0.7919142898975839</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912777863980647</v>
+        <v>0.7912766499077406</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926377930866955</v>
+        <v>0.7926359940244928</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913103406317563</v>
+        <v>0.7913084889755919</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898568615196229</v>
+        <v>0.7898549818626962</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882796077569751</v>
+        <v>0.7882777375838576</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7871980644496259</v>
+        <v>0.7871962287327283</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7891976395814675</v>
+        <v>0.7891954815899123</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944814896330464</v>
+        <v>0.7944804931264511</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968966349678492</v>
+        <v>0.7968955776978199</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993238656226007</v>
+        <v>0.7993227841640694</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001614708441507</v>
+        <v>0.8001609530565932</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.798674741535796</v>
+        <v>0.7986750838620041</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992808259705498</v>
+        <v>0.7992815033032316</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039637242377772</v>
+        <v>0.8039633794628203</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095892812884206</v>
+        <v>0.8095878668813248</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157469446444846</v>
+        <v>0.8157449811942222</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221489115239337</v>
+        <v>0.8221473304498853</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229330445631449</v>
+        <v>0.8229326725430285</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188191211201425</v>
+        <v>0.8188206365203856</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153777026619662</v>
+        <v>0.8153798185602568</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140568618642712</v>
+        <v>0.8140608303877397</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124923033032959</v>
+        <v>0.81249870279202</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123994980857486</v>
+        <v>0.8124077074739861</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176555123789344</v>
+        <v>0.8176656158621027</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233818047186732</v>
+        <v>0.8233931025219758</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.830294005714336</v>
+        <v>0.8303065790156405</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8350025062973072</v>
+        <v>0.835016499716083</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.820201458304475</v>
+        <v>0.8202174826979933</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.822022954728834</v>
+        <v>0.8220389487222329</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8095009567381725</v>
+        <v>0.8095184214318991</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.801361780326017</v>
+        <v>0.8013782613257321</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7942225519481403</v>
+        <v>0.7942415827134992</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7846751138020283</v>
+        <v>0.7846955903227448</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688852333142875</v>
+        <v>0.7688933674903632</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665944440931393</v>
+        <v>0.7666001897241433</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583514312880794</v>
+        <v>0.7583518134959002</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7474852991468997</v>
+        <v>0.7474776225934262</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7384610798690733</v>
+        <v>0.7384487343316888</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7287372472856536</v>
+        <v>0.7287195503404664</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7325439674678274</v>
+        <v>0.7325144207305588</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7378930471893117</v>
+        <v>0.7378615010175418</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7475382110208726</v>
+        <v>0.7475093770014761</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7563246135814632</v>
+        <v>0.7562965007789619</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727193608207139</v>
+        <v>0.7727070198146779</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771608037328452</v>
+        <v>0.7771526928176102</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.777669344963837</v>
+        <v>0.7776595552200458</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831717811452523</v>
+        <v>0.7831663117299691</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.78853459940487</v>
+        <v>0.788533341474285</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923573139770019</v>
+        <v>0.792357964210114</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892783694065669</v>
+        <v>0.7892747292877341</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918647146567173</v>
+        <v>0.7918587081906379</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971230964790603</v>
+        <v>0.7971123907374555</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8021045132903396</v>
+        <v>0.8020901802236793</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8047415398200637</v>
+        <v>0.8047272299223239</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073597531215655</v>
+        <v>0.8073469783930117</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096332177634098</v>
+        <v>0.8096227721795064</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095561512659892</v>
+        <v>0.8095528359406643</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089907469016138</v>
+        <v>0.8089944589407851</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096051663843729</v>
+        <v>0.8096089568951003</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105474377592972</v>
+        <v>0.8105495377973065</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140075843351995</v>
+        <v>0.8140091582936182</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190203208836666</v>
+        <v>0.8190221486102844</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8228893099760829</v>
+        <v>0.8230292735293046</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8257313135115877</v>
+        <v>0.8258447590199796</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8292904022591261</v>
+        <v>0.8293991553374203</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8324365965340015</v>
+        <v>0.8325821046165152</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8335677698962605</v>
+        <v>0.8337753700248487</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8340051005029304</v>
+        <v>0.8342856995973089</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8345230481614975</v>
+        <v>0.834858500084006</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8348179353603471</v>
+        <v>0.8352043521808609</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8391348196694381</v>
+        <v>0.8394480911313734</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8439195608437738</v>
+        <v>0.8442279877407179</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8491271513477077</v>
+        <v>0.8493899447844964</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8549513368143051</v>
+        <v>0.8551095441699028</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8569986620486203</v>
+        <v>0.8573693459396703</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8650103673233832</v>
+        <v>0.8651191616643839</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886163645680067</v>
+        <v>0.788615795962657</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919142898975839</v>
+        <v>0.7919131898471696</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912766499077406</v>
+        <v>0.7912755325531433</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926359940244928</v>
+        <v>0.7926342253306594</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913084889755919</v>
+        <v>0.791306668582184</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898549818626962</v>
+        <v>0.7898531339507053</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882777375838576</v>
+        <v>0.7882758990005614</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7871962287327283</v>
+        <v>0.7871944240236165</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7891954815899123</v>
+        <v>0.7891933599913227</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944804931264511</v>
+        <v>0.7944795135056807</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968955776978199</v>
+        <v>0.7968945383558358</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993227841640694</v>
+        <v>0.799321721055767</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001609530565932</v>
+        <v>0.8001604438718509</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986750838620041</v>
+        <v>0.7986754201584169</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992815033032316</v>
+        <v>0.7992821690785278</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039633794628203</v>
+        <v>0.8039630403400565</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095878668813248</v>
+        <v>0.8095864759395873</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157449811942222</v>
+        <v>0.8157430497311691</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221473304498853</v>
+        <v>0.8221457748101275</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229326725430285</v>
+        <v>0.8229323053589063</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188206365203856</v>
+        <v>0.8188221243422051</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153798185602568</v>
+        <v>0.815381896616452</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140608303877397</v>
+        <v>0.8140647297943044</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.81249870279202</v>
+        <v>0.8125049917270936</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8124077074739861</v>
+        <v>0.8124157757916329</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176656158621027</v>
+        <v>0.8176755463140014</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233931025219758</v>
+        <v>0.8234042074964494</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8303065790156405</v>
+        <v>0.8303189383029137</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.835016499716083</v>
+        <v>0.835030259759702</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8202174826979933</v>
+        <v>0.8202332369836782</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8220389487222329</v>
+        <v>0.822054673600634</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8095184214318991</v>
+        <v>0.809535591350985</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8013782613257321</v>
+        <v>0.8013944647771212</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7942415827134992</v>
+        <v>0.7942602941028478</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7846955903227448</v>
+        <v>0.7847157257236241</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688933674903632</v>
+        <v>0.7689013692867517</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7666001897241433</v>
+        <v>0.7666058455826135</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583518134959002</v>
+        <v>0.7583521983494929</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7474776225934262</v>
+        <v>0.7474700848383401</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7384487343316888</v>
+        <v>0.73843660804047</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7287195503404664</v>
+        <v>0.7287021610980458</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7325144207305588</v>
+        <v>0.732485371975181</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7378615010175418</v>
+        <v>0.737830483852442</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7475093770014761</v>
+        <v>0.747481021765166</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7562965007789619</v>
+        <v>0.7562688494359344</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727070198146779</v>
+        <v>0.7726948806717471</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771526928176102</v>
+        <v>0.7771447124340316</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776595552200458</v>
+        <v>0.7776499240585257</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831663117299691</v>
+        <v>0.7831609314551518</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.788533341474285</v>
+        <v>0.7885321067526223</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.792357964210114</v>
+        <v>0.792358609734126</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892747292877341</v>
+        <v>0.7892711541271636</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918587081906379</v>
+        <v>0.7918528067324107</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971123907374555</v>
+        <v>0.7971018648725593</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8020901802236793</v>
+        <v>0.8020760840421954</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8047272299223239</v>
+        <v>0.8047131516036123</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073469783930117</v>
+        <v>0.807334401529908</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096227721795064</v>
+        <v>0.8096124792981017</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095528359406643</v>
+        <v>0.8095495467624829</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089944589407851</v>
+        <v>0.8089980871514332</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096089568951003</v>
+        <v>0.8096126745820387</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105495377973065</v>
+        <v>0.8105516018252892</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140091582936182</v>
+        <v>0.8140107300783768</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190221486102844</v>
+        <v>0.8190240006235353</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8230292735293046</v>
+        <v>0.8230291365309328</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8258447590199796</v>
+        <v>0.8259986947245903</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8293991553374203</v>
+        <v>0.8295055689828895</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8325821046165152</v>
+        <v>0.8326550580686043</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8337753700248487</v>
+        <v>0.833933183959932</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8342856995973089</v>
+        <v>0.834465814848581</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.834858500084006</v>
+        <v>0.8350863709883708</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8352043521808609</v>
+        <v>0.8355255611981163</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8394480911313734</v>
+        <v>0.8397679873221527</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8442279877407179</v>
+        <v>0.8445144359244283</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8493899447844964</v>
+        <v>0.849672399396638</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8551095441699028</v>
+        <v>0.8551122574804967</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8573693459396703</v>
+        <v>0.8571626565116364</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,15 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8651191616643839</v>
+        <v>0.8636944377654319</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B85">
+        <v>0.8578871248947089</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8295055689828895</v>
+        <v>0.8295055912601343</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8326550580686043</v>
+        <v>0.8326550441011051</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.833933183959932</v>
+        <v>0.8338986769694587</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.834465814848581</v>
+        <v>0.8344372764702738</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8350863709883708</v>
+        <v>0.8350649642679761</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8355255611981163</v>
+        <v>0.8355092820916412</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8397679873221527</v>
+        <v>0.8397553878313857</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8445144359244283</v>
+        <v>0.8445044610210105</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.849672399396638</v>
+        <v>0.8496621592657991</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8551122574804967</v>
+        <v>0.8551033690849572</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8571626565116364</v>
+        <v>0.8571547407442843</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8636944377654319</v>
+        <v>0.8636852973519786</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8578871248947089</v>
+        <v>0.8578484911466333</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788615795962657</v>
+        <v>0.7886152369130193</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919131898471696</v>
+        <v>0.791912108256331</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912755325531433</v>
+        <v>0.7912744338550675</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926342253306594</v>
+        <v>0.7926324862427856</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.791306668582184</v>
+        <v>0.7913048786665053</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898531339507053</v>
+        <v>0.7898513169862802</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882758990005614</v>
+        <v>0.7882740912134862</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7871944240236165</v>
+        <v>0.7871926495433124</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7891933599913227</v>
+        <v>0.7891912738729472</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944795135056807</v>
+        <v>0.7944785503451968</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968945383558358</v>
+        <v>0.7968935164897785</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799321721055767</v>
+        <v>0.7993206758346277</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001604438718509</v>
+        <v>0.8001599430774426</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986754201584169</v>
+        <v>0.7986757505826714</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992821690785278</v>
+        <v>0.7992828235896345</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039630403400565</v>
+        <v>0.8039627067318709</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095864759395873</v>
+        <v>0.8095851078846534</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157430497311691</v>
+        <v>0.8157411494817641</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221457748101275</v>
+        <v>0.8221442439979187</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229323053589063</v>
+        <v>0.822931942925659</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188221243422051</v>
+        <v>0.8188235853274701</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.815381896616452</v>
+        <v>0.8153839378327569</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140647297943044</v>
+        <v>0.8140685618704919</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8125049917270936</v>
+        <v>0.8125111729441958</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8124157757916329</v>
+        <v>0.8124237066383039</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176755463140014</v>
+        <v>0.8176853081348421</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8234042074964494</v>
+        <v>0.8234151245287652</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8303189383029137</v>
+        <v>0.8303310889846063</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.835030259759702</v>
+        <v>0.8350437922129935</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8202332369836782</v>
+        <v>0.8202487279292786</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.822054673600634</v>
+        <v>0.8220701360947587</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.809535591350985</v>
+        <v>0.8095524738891817</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8013944647771212</v>
+        <v>0.8014103976257354</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7942602941028478</v>
+        <v>0.794278694079019</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7847157257236241</v>
+        <v>0.7847355284439346</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7689013692867517</v>
+        <v>0.7689092418987536</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7666058455826135</v>
+        <v>0.7666114137376232</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583521983494929</v>
+        <v>0.7583525855538548</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7474700848383401</v>
+        <v>0.7474626821702818</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.73843660804047</v>
+        <v>0.7384246952272234</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7287021610980458</v>
+        <v>0.7286850716175328</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.732485371975181</v>
+        <v>0.7324568087318457</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.737830483852442</v>
+        <v>0.7377999825166701</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.747481021765166</v>
+        <v>0.7474531335037946</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7562688494359344</v>
+        <v>0.7562416483044476</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7726948806717471</v>
+        <v>0.7726829384885252</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771447124340316</v>
+        <v>0.7771368594652514</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776499240585257</v>
+        <v>0.777640447665527</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831609314551518</v>
+        <v>0.7831556381614202</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885321067526223</v>
+        <v>0.7885308946066392</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.792358609734126</v>
+        <v>0.7923592505112973</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892711541271636</v>
+        <v>0.7892676422074023</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918528067324107</v>
+        <v>0.7918470075594155</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971018648725593</v>
+        <v>0.7970915144026272</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8020760840421954</v>
+        <v>0.802062218946032</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8047131516036123</v>
+        <v>0.8046992993246449</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.807334401529908</v>
+        <v>0.8073220180292161</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096124792981017</v>
+        <v>0.8096023358791687</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095495467624829</v>
+        <v>0.809546283788434</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8089980871514332</v>
+        <v>0.8090016340835076</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096126745820387</v>
+        <v>0.8096163213958296</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105516018252892</v>
+        <v>0.8105536306606609</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140107300783768</v>
+        <v>0.8140122990787542</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190240006235353</v>
+        <v>0.8190258750110728</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8230291365309328</v>
+        <v>0.8230290602734934</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8259986947245903</v>
+        <v>0.8261825991531258</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8295055912601343</v>
+        <v>0.8296549419491444</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8326550441011051</v>
+        <v>0.8327907897838941</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8338986769694587</v>
+        <v>0.8341004619766367</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8344372764702738</v>
+        <v>0.8346798214811433</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8350649642679761</v>
+        <v>0.8353708431923919</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8355092820916412</v>
+        <v>0.8359144198863248</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8397553878313857</v>
+        <v>0.8401670990848094</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8445044610210105</v>
+        <v>0.8448982326816787</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8496621592657991</v>
+        <v>0.8500918373936244</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8551033690849572</v>
+        <v>0.855351525915486</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8571547407442843</v>
+        <v>0.8573475267009696</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8636852973519786</v>
+        <v>0.8633076115957343</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8578484911466333</v>
+        <v>0.8606955640519199</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886152369130193</v>
+        <v>0.7886206342543632</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791912108256331</v>
+        <v>0.7919225493344517</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912744338550675</v>
+        <v>0.7912850362053001</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926324862427856</v>
+        <v>0.7926492713676951</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913048786665053</v>
+        <v>0.7913221546291659</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898513169862802</v>
+        <v>0.7898688543960493</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882740912134862</v>
+        <v>0.7882915402454895</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7871926495433124</v>
+        <v>0.7872097770924973</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7891912738729472</v>
+        <v>0.7892114070550863</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944785503451968</v>
+        <v>0.7944878490538261</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968935164897785</v>
+        <v>0.7969033824676099</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993206758346277</v>
+        <v>0.7993307677839376</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001599430774426</v>
+        <v>0.800164771078977</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986757505826714</v>
+        <v>0.7986725513753636</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992828235896345</v>
+        <v>0.7992765014984419</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039627067318709</v>
+        <v>0.8039659198958719</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095851078846534</v>
+        <v>0.8095982954872507</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157411494817641</v>
+        <v>0.8157594437755529</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221442439979187</v>
+        <v>0.8221589686730626</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.822931942925659</v>
+        <v>0.8229353832137322</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188235853274701</v>
+        <v>0.818809404401</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153839378327569</v>
+        <v>0.8153641516409654</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140685618704919</v>
+        <v>0.8140314908310853</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8125111729441958</v>
+        <v>0.8124514127320241</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8124237066383039</v>
+        <v>0.81234706101535</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176853081348421</v>
+        <v>0.8175909910967744</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8234151245287652</v>
+        <v>0.8233096723669662</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8303310889846063</v>
+        <v>0.8302137439436622</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8350437922129935</v>
+        <v>0.8349132949578555</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8202487279292786</v>
+        <v>0.8200992299062995</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8220701360947587</v>
+        <v>0.8219209318838061</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8095524738891817</v>
+        <v>0.8093895306026146</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8014103976257354</v>
+        <v>0.8012566453294527</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.794278694079019</v>
+        <v>0.7941011785448384</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7847355284439346</v>
+        <v>0.7845445807521627</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7689092418987536</v>
+        <v>0.7688334554358253</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7666114137376232</v>
+        <v>0.7665579607164483</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583525855538548</v>
+        <v>0.7583492126047882</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7474626821702818</v>
+        <v>0.7475344990987333</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7384246952272234</v>
+        <v>0.7385401078546117</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7286850716175328</v>
+        <v>0.7288503726406905</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7324568087318457</v>
+        <v>0.7327324604647386</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7377999825166701</v>
+        <v>0.7380942307893896</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7474531335037946</v>
+        <v>0.7477219835710099</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7562416483044476</v>
+        <v>0.756503660506211</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7726829384885252</v>
+        <v>0.7727979421048401</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771368594652514</v>
+        <v>0.7772123983520198</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.777640447665527</v>
+        <v>0.7777316437847314</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831556381614202</v>
+        <v>0.7832065999773777</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885308946066392</v>
+        <v>0.7885426729817666</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923592505112973</v>
+        <v>0.7923533167403936</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892676422074023</v>
+        <v>0.7893016786755055</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918470075594155</v>
+        <v>0.79190312390675</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7970915144026272</v>
+        <v>0.7971913795179804</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.802062218946032</v>
+        <v>0.8007488885928005</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8046992993246449</v>
+        <v>0.8041262142602971</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8073220180292161</v>
+        <v>0.8068458241855365</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8096023358791687</v>
+        <v>0.809080471827299</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.809546283788434</v>
+        <v>0.8095969486789942</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8090016340835076</v>
+        <v>0.8094364657972068</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096163213958296</v>
+        <v>0.8097339594912676</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105536306606609</v>
+        <v>0.8103634948436236</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140122990787542</v>
+        <v>0.8142960372543373</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190258750110728</v>
+        <v>0.8195109894794619</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8230290602734934</v>
+        <v>0.8243204808603439</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8261825991531258</v>
+        <v>0.8285298840448954</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8296549419491444</v>
+        <v>0.832304850754742</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8327907897838941</v>
+        <v>0.8364351565215646</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8341004619766367</v>
+        <v>0.8378492754153848</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8346798214811433</v>
+        <v>0.838796746058068</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8353708431923919</v>
+        <v>0.8400696052831742</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8359144198863248</v>
+        <v>0.8417626476783309</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8401670990848094</v>
+        <v>0.8486910250803468</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8448982326816787</v>
+        <v>0.8572027028868057</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8500918373936244</v>
+        <v>0.8675226359167555</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.855351525915486</v>
+        <v>0.8796042005024329</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8573475267009696</v>
+        <v>0.8809063359274149</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8633076115957343</v>
+        <v>0.8834535165186604</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8606955640519199</v>
+        <v>0.8786621150973289</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886206342543632</v>
+        <v>0.7886141465332933</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919225493344517</v>
+        <v>0.791909998625558</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912850362053001</v>
+        <v>0.7912722905903392</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926492713676951</v>
+        <v>0.7926290939607662</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913221546291659</v>
+        <v>0.7913013872574661</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898688543960493</v>
+        <v>0.7898477728419553</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882915402454895</v>
+        <v>0.7882705649843053</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872097770924973</v>
+        <v>0.7871891882815136</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892114070550863</v>
+        <v>0.7891872045759126</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944878490538261</v>
+        <v>0.7944766717732361</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969033824676099</v>
+        <v>0.796891523451715</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993307677839376</v>
+        <v>0.7993186372781785</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800164771078977</v>
+        <v>0.8001589658440987</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986725513753636</v>
+        <v>0.7986763944182961</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992765014984419</v>
+        <v>0.7992840999433199</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039659198958719</v>
+        <v>0.8039620555307141</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095982954872507</v>
+        <v>0.809582438214442</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157594437755529</v>
+        <v>0.8157374396520938</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221589686730626</v>
+        <v>0.8221412545238163</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229353832137322</v>
+        <v>0.8229312319793937</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818809404401</v>
+        <v>0.8188264296257334</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153641516409654</v>
+        <v>0.8153879135812351</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140314908310853</v>
+        <v>0.8140760308757498</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124514127320241</v>
+        <v>0.8125232230911658</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.81234706101535</v>
+        <v>0.8124391697159713</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8175909910967744</v>
+        <v>0.8177043427517472</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233096723669662</v>
+        <v>0.8234364135030419</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8302137439436622</v>
+        <v>0.8303547852704695</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349132949578555</v>
+        <v>0.8350701965483162</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8200992299062995</v>
+        <v>0.8202789457600577</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219209318838061</v>
+        <v>0.8221002997499808</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8093895306026146</v>
+        <v>0.8095854051829554</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8012566453294527</v>
+        <v>0.801441478158245</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941011785448384</v>
+        <v>0.7943145903428481</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7845445807521627</v>
+        <v>0.7847741682329337</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688334554358253</v>
+        <v>0.76892461184647</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665579607164483</v>
+        <v>0.7666222949036736</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583492126047882</v>
+        <v>0.7583533659207243</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475344990987333</v>
+        <v>0.7474482678969261</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7385401078546117</v>
+        <v>0.7384014879529672</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7288503726406905</v>
+        <v>0.7286517615195206</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7327324604647386</v>
+        <v>0.7324010909471045</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7380942307893896</v>
+        <v>0.7377404767732868</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7477219835710099</v>
+        <v>0.7473987125803132</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.756503660506211</v>
+        <v>0.7561885534794019</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727979421048401</v>
+        <v>0.7726596261675093</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772123983520198</v>
+        <v>0.7771215237915637</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777316437847314</v>
+        <v>0.7776219445305059</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832065999773777</v>
+        <v>0.7831453042225359</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885426729817666</v>
+        <v>0.7885285356213626</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923533167403936</v>
+        <v>0.7923605177055711</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7893016786755055</v>
+        <v>0.7892608015170609</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.79190312390675</v>
+        <v>0.7918357056401364</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971913795179804</v>
+        <v>0.7970713224507231</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8007488885928005</v>
+        <v>0.8020351597377644</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8041262142602971</v>
+        <v>0.804672251592164</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8068458241855365</v>
+        <v>0.8072978137660216</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.809080471827299</v>
+        <v>0.8095824849059117</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095969486789942</v>
+        <v>0.8095398365617386</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8094364657972068</v>
+        <v>0.8090084938336355</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8097339594912676</v>
+        <v>0.8096234098809278</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8103634948436236</v>
+        <v>0.8105575859173746</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8142960372543373</v>
+        <v>0.8140154264971724</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8195109894794619</v>
+        <v>0.8190296837680183</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8243204808603439</v>
+        <v>0.8230290788701815</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8285298840448954</v>
+        <v>0.8264051960064017</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.832304850754742</v>
+        <v>0.8297703080223866</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8364351565215646</v>
+        <v>0.8328108158715282</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8378492754153848</v>
+        <v>0.8341830201283638</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.838796746058068</v>
+        <v>0.8347762510235643</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8400696052831742</v>
+        <v>0.8355399629331736</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8417626476783309</v>
+        <v>0.8362404143280678</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8486910250803468</v>
+        <v>0.8404794235639301</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8572027028868057</v>
+        <v>0.8451267094086479</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8675226359167555</v>
+        <v>0.8502173846244934</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8796042005024329</v>
+        <v>0.8548996720797473</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8809063359274149</v>
+        <v>0.85639495406003</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8834535165186604</v>
+        <v>0.8606247424421622</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8786621150973289</v>
+        <v>0.8565913260575113</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886141465332933</v>
+        <v>0.7886199913312567</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791909998625558</v>
+        <v>0.7919213057419603</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912722905903392</v>
+        <v>0.7912837738577955</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926290939607662</v>
+        <v>0.7926472725219821</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913013872574661</v>
+        <v>0.7913200973014868</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898477728419553</v>
+        <v>0.789866765889495</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882705649843053</v>
+        <v>0.7882894622400325</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7871891882815136</v>
+        <v>0.7872077373725316</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7891872045759126</v>
+        <v>0.7892090096693013</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944766717732361</v>
+        <v>0.7944867414201271</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.796891523451715</v>
+        <v>0.7969022072035623</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993186372781785</v>
+        <v>0.7993295655451673</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001589658440987</v>
+        <v>0.8001641967849217</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986763944182961</v>
+        <v>0.7986729335278553</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992840999433199</v>
+        <v>0.7992772549402239</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039620555307141</v>
+        <v>0.803965538045663</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.809582438214442</v>
+        <v>0.8095967269770141</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157374396520938</v>
+        <v>0.81575727063954</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221412545238163</v>
+        <v>0.822157221080749</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229312319793937</v>
+        <v>0.8229349802978656</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188264296257334</v>
+        <v>0.818811102481898</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153879135812351</v>
+        <v>0.8153665178072915</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140760308757498</v>
+        <v>0.8140359153457326</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8125232230911658</v>
+        <v>0.8124585410320493</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8124391697159713</v>
+        <v>0.812356199916723</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8177043427517472</v>
+        <v>0.8176022343029945</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8234364135030419</v>
+        <v>0.8233222398639697</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8303547852704695</v>
+        <v>0.830227726050522</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8350701965483162</v>
+        <v>0.8349288217911988</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8202789457600577</v>
+        <v>0.8201170309017275</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8221002997499808</v>
+        <v>0.8219386956411465</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8095854051829554</v>
+        <v>0.8094089343382171</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.801441478158245</v>
+        <v>0.8012749516463787</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7943145903428481</v>
+        <v>0.7941223089616093</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7847741682329337</v>
+        <v>0.7845672982056532</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.76892461184647</v>
+        <v>0.7688424572402363</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7666222949036736</v>
+        <v>0.7665642922482763</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583533659207243</v>
+        <v>0.7583495716216728</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7474482678969261</v>
+        <v>0.7475259037084542</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7384014879529672</v>
+        <v>0.7385263133101233</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7286517615195206</v>
+        <v>0.728830645980437</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7324010909471045</v>
+        <v>0.7326996385143627</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7377404767732868</v>
+        <v>0.7380592071167559</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7473987125803132</v>
+        <v>0.7476900051884512</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7561885534794019</v>
+        <v>0.75647252046806</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7726596261675093</v>
+        <v>0.7727842772757691</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771215237915637</v>
+        <v>0.7772034327659664</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776219445305059</v>
+        <v>0.7777208150200009</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831453042225359</v>
+        <v>0.7832005461202092</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885285356213626</v>
+        <v>0.7885412610850713</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923605177055711</v>
+        <v>0.7923539940094557</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892608015170609</v>
+        <v>0.7892976090284893</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918357056401364</v>
+        <v>0.7918964244541313</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7970713224507231</v>
+        <v>0.7971794913222838</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8020351597377644</v>
+        <v>0.8007343663953891</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.804672251592164</v>
+        <v>0.8041110710877569</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8072978137660216</v>
+        <v>0.8068318438071633</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8095824849059117</v>
+        <v>0.8090685631065959</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095398365617386</v>
+        <v>0.8095917639817982</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8090084938336355</v>
+        <v>0.8094387029836476</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096234098809278</v>
+        <v>0.8097372857344358</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105575859173746</v>
+        <v>0.8103657198158598</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140154264971724</v>
+        <v>0.8142978528034701</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190296837680183</v>
+        <v>0.819514744117432</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8230290788701815</v>
+        <v>0.8243213979659215</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8264051960064017</v>
+        <v>0.8285467105245727</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8297703080223866</v>
+        <v>0.83226131748264</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8328108158715282</v>
+        <v>0.8362582682345465</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8341830201283638</v>
+        <v>0.8376899242789559</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8347762510235643</v>
+        <v>0.8386156546765466</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8355399629331736</v>
+        <v>0.8398643449760441</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8362404143280678</v>
+        <v>0.8415388445392116</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8404794235639301</v>
+        <v>0.8483091309872948</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8451267094086479</v>
+        <v>0.8566015585011114</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8502173846244934</v>
+        <v>0.8666674472034814</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8548996720797473</v>
+        <v>0.878193319624641</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.85639495406003</v>
+        <v>0.8793742859686875</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8606247424421622</v>
+        <v>0.8815529136508741</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8565913260575113</v>
+        <v>0.8772014034915343</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886199913312567</v>
+        <v>0.7886136147488277</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919213057419603</v>
+        <v>0.7919089697091077</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912837738577955</v>
+        <v>0.791271245142034</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926472725219821</v>
+        <v>0.7926274393642176</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913200973014868</v>
+        <v>0.7912996843201248</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789866765889495</v>
+        <v>0.7898460441954074</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882894622400325</v>
+        <v>0.7882688450825038</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872077373725316</v>
+        <v>0.7871875000672187</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892090096693013</v>
+        <v>0.7891852197181586</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944867414201271</v>
+        <v>0.7944757555792579</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969022072035623</v>
+        <v>0.7968905514483793</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993295655451673</v>
+        <v>0.7993176430914566</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001641967849217</v>
+        <v>0.8001584890137687</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986729335278553</v>
+        <v>0.7986767081186664</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992772549402239</v>
+        <v>0.799284722324751</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.803965538045663</v>
+        <v>0.8039617376839323</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095967269770141</v>
+        <v>0.8095811355332747</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.81575727063954</v>
+        <v>0.8157356286442681</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.822157221080749</v>
+        <v>0.8221397947408826</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229349802978656</v>
+        <v>0.8229308833041649</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818811102481898</v>
+        <v>0.8188278142957669</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153665178072915</v>
+        <v>0.8153898499489804</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140359153457326</v>
+        <v>0.814079671083363</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124585410320493</v>
+        <v>0.8125290972282273</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.812356199916723</v>
+        <v>0.8124467085599094</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176022343029945</v>
+        <v>0.8177136236338963</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233222398639697</v>
+        <v>0.8234467944277508</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.830227726050522</v>
+        <v>0.8303663408189368</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349288217911988</v>
+        <v>0.8350830790830982</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8201170309017275</v>
+        <v>0.8202936850966963</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219386956411465</v>
+        <v>0.822115013296315</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8094089343382171</v>
+        <v>0.8096014675407537</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8012749516463787</v>
+        <v>0.8014566386223874</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941223089616093</v>
+        <v>0.7943321012874147</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7845672982056532</v>
+        <v>0.7847930208460607</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688424572402363</v>
+        <v>0.7689321150802616</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665642922482763</v>
+        <v>0.7666276117498042</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583495716216728</v>
+        <v>0.758353758576062</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475259037084542</v>
+        <v>0.7474412494993128</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7385263133101233</v>
+        <v>0.7383901829214141</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.728830645980437</v>
+        <v>0.7286355263274126</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7326996385143627</v>
+        <v>0.7323739134613509</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7380592071167559</v>
+        <v>0.7377114481084371</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7476900051884512</v>
+        <v>0.7473721581631881</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.75647252046806</v>
+        <v>0.7561626390424705</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727842772757691</v>
+        <v>0.7726482469843865</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7772034327659664</v>
+        <v>0.777114035328567</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777208150200009</v>
+        <v>0.7776129107473628</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7832005461202092</v>
+        <v>0.7831402595933752</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885412610850713</v>
+        <v>0.7885273876252424</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923539940094557</v>
+        <v>0.7923611440772294</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892976090284893</v>
+        <v>0.7892574696005472</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918964244541313</v>
+        <v>0.791830197898497</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971794913222838</v>
+        <v>0.7970614727176683</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8007343663953891</v>
+        <v>0.802021954931494</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8041110710877569</v>
+        <v>0.8046590459035652</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8068318438071633</v>
+        <v>0.8072859846462646</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8090685631065959</v>
+        <v>0.8095727713004304</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095917639817982</v>
+        <v>0.8095366523095198</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8094387029836476</v>
+        <v>0.8090118112862732</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8097372857344358</v>
+        <v>0.8096268551356383</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8103657198158598</v>
+        <v>0.8105595138692713</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8142978528034701</v>
+        <v>0.8140169838994404</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.819514744117432</v>
+        <v>0.8190316148045249</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8243213979659215</v>
+        <v>0.8230291684842859</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8285467105245727</v>
+        <v>0.8264690310797129</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.83226131748264</v>
+        <v>0.8297697484165003</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8362582682345465</v>
+        <v>0.8327433964384555</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8376899242789559</v>
+        <v>0.8341204094115793</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8386156546765466</v>
+        <v>0.8346983718540908</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8398643449760441</v>
+        <v>0.8354847114702919</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8415388445392116</v>
+        <v>0.8362546011725036</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8483091309872948</v>
+        <v>0.8404851403775921</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8566015585011114</v>
+        <v>0.8450837296238982</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8666674472034814</v>
+        <v>0.8500839027935544</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.878193319624641</v>
+        <v>0.8544396930060763</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8793742859686875</v>
+        <v>0.8556160597387079</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8815529136508741</v>
+        <v>0.8590042641075389</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8772014034915343</v>
+        <v>0.8543077803133854</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8297697484165003</v>
+        <v>0.8297692447234908</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8327433964384555</v>
+        <v>0.8327393000950323</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8341204094115793</v>
+        <v>0.8340947374898389</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8346983718540908</v>
+        <v>0.8346926035362858</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8354847114702919</v>
+        <v>0.8354787795103342</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8362546011725036</v>
+        <v>0.8362490566614907</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8404851403775921</v>
+        <v>0.840480143725136</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8450837296238982</v>
+        <v>0.8450788267980833</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8500839027935544</v>
+        <v>0.8500765116238562</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8544396930060763</v>
+        <v>0.8544270235966434</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8556160597387079</v>
+        <v>0.8555948352421718</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8590042641075389</v>
+        <v>0.8589666688742758</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8543077803133854</v>
+        <v>0.8542233430815365</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886136147488277</v>
+        <v>0.7886193598879965</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919089697091077</v>
+        <v>0.791920084319675</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.791271245142034</v>
+        <v>0.7912825338954282</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926274393642176</v>
+        <v>0.7926453092160846</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7912996843201248</v>
+        <v>0.7913180765615643</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898460441954074</v>
+        <v>0.7898647145368076</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882688450825038</v>
+        <v>0.7882874212078691</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7871875000672187</v>
+        <v>0.7872057339446332</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7891852197181586</v>
+        <v>0.7892066548668497</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944757555792579</v>
+        <v>0.7944856535601038</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968905514483793</v>
+        <v>0.7969010529360669</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993176430914566</v>
+        <v>0.799328384799695</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001584890137687</v>
+        <v>0.8001636325318287</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986767081186664</v>
+        <v>0.7986733085758393</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.799284722324751</v>
+        <v>0.7992779948332529</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039617376839323</v>
+        <v>0.8039651627772464</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095811355332747</v>
+        <v>0.8095951858469526</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157356286442681</v>
+        <v>0.8157551347114289</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221397947408826</v>
+        <v>0.8221555030099996</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229308833041649</v>
+        <v>0.8229345827633898</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188278142957669</v>
+        <v>0.8188127679093694</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153898499489804</v>
+        <v>0.8153688392888367</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.814079671083363</v>
+        <v>0.8140402585823121</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8125290972282273</v>
+        <v>0.8124655394942266</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8124467085599094</v>
+        <v>0.8123651732847503</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8177136236338963</v>
+        <v>0.8176132745877227</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8234467944277508</v>
+        <v>0.8233345813529502</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8303663408189368</v>
+        <v>0.8302414574351271</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8350830790830982</v>
+        <v>0.8349440760787669</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8202936850966963</v>
+        <v>0.8201345158989124</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.822115013296315</v>
+        <v>0.8219561446549299</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8096014675407537</v>
+        <v>0.809427993158734</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8014566386223874</v>
+        <v>0.801292933328658</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7943321012874147</v>
+        <v>0.7941430660469234</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7847930208460607</v>
+        <v>0.7845896174157405</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7689321150802616</v>
+        <v>0.7688513051080761</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7666276117498042</v>
+        <v>0.7665705201386888</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.758353758576062</v>
+        <v>0.7583499354862837</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7474412494993128</v>
+        <v>0.7475174724855642</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7383901829214141</v>
+        <v>0.738512777361191</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7286355263274126</v>
+        <v>0.7288112810664542</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7323739134613509</v>
+        <v>0.7326673990884809</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7377114481084371</v>
+        <v>0.7380248017267883</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7473721581631881</v>
+        <v>0.7476585854856687</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7561626390424705</v>
+        <v>0.7564419178799696</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7726482469843865</v>
+        <v>0.7727708474228887</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.777114035328567</v>
+        <v>0.7771946187126222</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776129107473628</v>
+        <v>0.7777101705591376</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831402595933752</v>
+        <v>0.7831945959830159</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885273876252424</v>
+        <v>0.7885398767379455</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923611440772294</v>
+        <v>0.7923546669610417</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892574696005472</v>
+        <v>0.7892936160638779</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.791830197898497</v>
+        <v>0.7918898485484406</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7970614727176683</v>
+        <v>0.7971678133605216</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.802021954931494</v>
+        <v>0.8007200975426549</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8046590459035652</v>
+        <v>0.8040961857010676</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8072859846462646</v>
+        <v>0.8068180925280843</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8095727713004304</v>
+        <v>0.809056840911757</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095366523095198</v>
+        <v>0.8095866388113377</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8090118112862732</v>
+        <v>0.8094408746345739</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096268551356383</v>
+        <v>0.8097405390034664</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105595138692713</v>
+        <v>0.8103679004560831</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8140169838994404</v>
+        <v>0.8142996557476883</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190316148045249</v>
+        <v>0.8195184829201994</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8230291684842859</v>
+        <v>0.8243223546406824</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8264690310797129</v>
+        <v>0.8285438956678384</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8297692447234908</v>
+        <v>0.8322547662721083</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8327393000950323</v>
+        <v>0.8361728145310939</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8340947374898389</v>
+        <v>0.837531115229216</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8346926035362858</v>
+        <v>0.8383920956626189</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8354787795103342</v>
+        <v>0.8396340686583449</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8362490566614907</v>
+        <v>0.84129165217617</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.840480143725136</v>
+        <v>0.8478957933447955</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8450788267980833</v>
+        <v>0.8559501153515801</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8500765116238562</v>
+        <v>0.8656397157055549</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8544270235966434</v>
+        <v>0.8766676771997204</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8555948352421718</v>
+        <v>0.8776562470063447</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8589666688742758</v>
+        <v>0.8793726750045665</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,15 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8542233430815365</v>
+        <v>0.8749347500788156</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B86">
+        <v>0.8686843937670863</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886193598879965</v>
+        <v>0.7886130916106878</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.791920084319675</v>
+        <v>0.7919079574979866</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912825338954282</v>
+        <v>0.791270216585737</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926453092160846</v>
+        <v>0.7926258115668905</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913180765615643</v>
+        <v>0.7912980089705606</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898647145368076</v>
+        <v>0.7898443435611057</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882874212078691</v>
+        <v>0.7882671530555194</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872057339446332</v>
+        <v>0.7871858392141544</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892066548668497</v>
+        <v>0.7891832669801208</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944856535601038</v>
+        <v>0.7944748542794761</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7969010529360669</v>
+        <v>0.796889595257156</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799328384799695</v>
+        <v>0.799316665087888</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001636325318287</v>
+        <v>0.8001580197904624</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986733085758393</v>
+        <v>0.7986770165253081</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992779948332529</v>
+        <v>0.7992853345204552</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039651627772464</v>
+        <v>0.8039614248437812</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095951858469526</v>
+        <v>0.8095798536057189</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157551347114289</v>
+        <v>0.8157338459931571</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221555030099996</v>
+        <v>0.822138357542038</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229345827633898</v>
+        <v>0.8229305390553513</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188127679093694</v>
+        <v>0.818829174845434</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153688392888367</v>
+        <v>0.8153917531507655</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140402585823121</v>
+        <v>0.8140832505224498</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124655394942266</v>
+        <v>0.8125348740691614</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123651732847503</v>
+        <v>0.8124541231681288</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176132745877227</v>
+        <v>0.8177227520685408</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233345813529502</v>
+        <v>0.8234570053883521</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8302414574351271</v>
+        <v>0.8303777076642354</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349440760787669</v>
+        <v>0.8350957553473348</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8201345158989124</v>
+        <v>0.8203081860132313</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219561446549299</v>
+        <v>0.8221294892457549</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.809427993158734</v>
+        <v>0.8096172697407729</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.801292933328658</v>
+        <v>0.8014715540617028</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941430660469234</v>
+        <v>0.7943493301524764</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7845896174157405</v>
+        <v>0.7848115718882021</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688513051080761</v>
+        <v>0.768939500933264</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665705201386888</v>
+        <v>0.7666328485669753</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583499354862837</v>
+        <v>0.7583541525659678</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475174724855642</v>
+        <v>0.7474343525936176</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.738512777361191</v>
+        <v>0.7383790702109005</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7288112810664542</v>
+        <v>0.7286195617268838</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7326673990884809</v>
+        <v>0.7323471755675822</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7380248017267883</v>
+        <v>0.7376828867256524</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7476585854856687</v>
+        <v>0.7473460271821605</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7564419178799696</v>
+        <v>0.7561371333035249</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727708474228887</v>
+        <v>0.7726370466587045</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771946187126222</v>
+        <v>0.7771066627570686</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7777101705591376</v>
+        <v>0.7776040176416473</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831945959830159</v>
+        <v>0.7831352939721816</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885398767379455</v>
+        <v>0.7885262598892897</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923546669610417</v>
+        <v>0.7923617656103124</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892936160638779</v>
+        <v>0.7892541946282103</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918898485484406</v>
+        <v>0.7918247824440902</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971678133605216</v>
+        <v>0.7970517818663073</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8007200975426549</v>
+        <v>0.8020089598083604</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8040961857010676</v>
+        <v>0.8046460457719894</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8068180925280843</v>
+        <v>0.8072743321653513</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.809056840911757</v>
+        <v>0.8095631950497389</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095866388113377</v>
+        <v>0.8095334942656007</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8094408746345739</v>
+        <v>0.8090150567375163</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8097405390034664</v>
+        <v>0.8096302366888903</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8103679004560831</v>
+        <v>0.8105614096907087</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8142996557476883</v>
+        <v>0.814018536480841</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8195184829201994</v>
+        <v>0.8190335615392035</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8243223546406824</v>
+        <v>0.8230293083467521</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8285438956678384</v>
+        <v>0.8264671366939711</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8322547662721083</v>
+        <v>0.8298216817322638</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8361728145310939</v>
+        <v>0.8327232955241912</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.837531115229216</v>
+        <v>0.8340108025369102</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8383920956626189</v>
+        <v>0.8344753910540335</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8396340686583449</v>
+        <v>0.8351713182904945</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.84129165217617</v>
+        <v>0.8358477102177366</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8478957933447955</v>
+        <v>0.8399234876768025</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8559501153515801</v>
+        <v>0.8444024051905696</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8656397157055549</v>
+        <v>0.8492414218730535</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8766676771997204</v>
+        <v>0.8532980594220237</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8776562470063447</v>
+        <v>0.8542315446807778</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8793726750045665</v>
+        <v>0.8567405485444484</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8749347500788156</v>
+        <v>0.8508416442902685</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46402</v>
       </c>
       <c r="B86">
-        <v>0.8686843937670863</v>
+        <v>0.8401953942902686</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.7886130916106878</v>
+        <v>0.7886187396198399</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919079574979866</v>
+        <v>0.7919188844800054</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.791270216585737</v>
+        <v>0.7912813157280801</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926258115668905</v>
+        <v>0.7926433805106173</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7912980089705606</v>
+        <v>0.7913160914421031</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.7898443435611057</v>
+        <v>0.7898626993554198</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882671530555194</v>
+        <v>0.7882854161710433</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7871858392141544</v>
+        <v>0.7872037658488644</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7891832669801208</v>
+        <v>0.7892043415233675</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944748542794761</v>
+        <v>0.794484584949006</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.796889595257156</v>
+        <v>0.7968999191075119</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.799316665087888</v>
+        <v>0.7993272249763262</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.8001580197904624</v>
+        <v>0.8001630780588519</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986770165253081</v>
+        <v>0.7986736767152184</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992853345204552</v>
+        <v>0.7992787215395836</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039614248437812</v>
+        <v>0.8039647939222445</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095798536057189</v>
+        <v>0.8095936713871419</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157338459931571</v>
+        <v>0.8157530350461994</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.822138357542038</v>
+        <v>0.822153813721911</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229305390553513</v>
+        <v>0.8229341905152396</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.818829174845434</v>
+        <v>0.8188144016106462</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153917531507655</v>
+        <v>0.8153711173341518</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140832505224498</v>
+        <v>0.8140445227552594</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8125348740691614</v>
+        <v>0.8124724116276957</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8124541231681288</v>
+        <v>0.8123739855688303</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8177227520685408</v>
+        <v>0.8176241173858574</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8234570053883521</v>
+        <v>0.8233467028648888</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8303777076642354</v>
+        <v>0.8302549447682088</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8350957553473348</v>
+        <v>0.8349590649272918</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8203081860132313</v>
+        <v>0.8201516932318094</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8221294892457549</v>
+        <v>0.8219732872102072</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8096172697407729</v>
+        <v>0.8094467161705936</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8014715540617028</v>
+        <v>0.8013105989261904</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7943493301524764</v>
+        <v>0.7941634595945255</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7848115718882021</v>
+        <v>0.7846115487436682</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.768939500933264</v>
+        <v>0.7688600029404311</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7666328485669753</v>
+        <v>0.7665766468861583</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583541525659678</v>
+        <v>0.7583503037734698</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7474343525936176</v>
+        <v>0.7475092007974757</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.7383790702109005</v>
+        <v>0.7384994928321393</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7286195617268838</v>
+        <v>0.7287922680593135</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7323471755675822</v>
+        <v>0.7326357268352841</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7376828867256524</v>
+        <v>0.7379909984161028</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7473460271821605</v>
+        <v>0.7476277099745089</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7561371333035249</v>
+        <v>0.7564118389765802</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7726370466587045</v>
+        <v>0.7727576465496652</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771066627570686</v>
+        <v>0.7771859523947982</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776040176416473</v>
+        <v>0.7776997057482857</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831352939721816</v>
+        <v>0.7831887469259095</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885262598892897</v>
+        <v>0.7885385191462296</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923617656103124</v>
+        <v>0.7923553355070398</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892541946282103</v>
+        <v>0.789289697642669</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.7918247824440902</v>
+        <v>0.7918833928131759</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7970517818663073</v>
+        <v>0.7971563401238073</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8020089598083604</v>
+        <v>0.8007060754894355</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8046460457719894</v>
+        <v>0.8040815516192088</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8072743321653513</v>
+        <v>0.8068045648316567</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8095631950497389</v>
+        <v>0.8090453009876859</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095334942656007</v>
+        <v>0.8095815724307718</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8090150567375163</v>
+        <v>0.8094429830813533</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8096302366888903</v>
+        <v>0.8097437214917724</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.8105614096907087</v>
+        <v>0.8103700379522849</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.814018536480841</v>
+        <v>0.8143014458337751</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8190335615392035</v>
+        <v>0.8195222050065463</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8230293083467521</v>
+        <v>0.8243233484826418</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8264671366939711</v>
+        <v>0.8285411636673223</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8298216817322638</v>
+        <v>0.8322756883625232</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8327232955241912</v>
+        <v>0.8361231498962665</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.8340108025369102</v>
+        <v>0.8374143247890128</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8344753910540335</v>
+        <v>0.8382170023014786</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.8351713182904945</v>
+        <v>0.8394494950284516</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8358477102177366</v>
+        <v>0.8410868710840884</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8399234876768025</v>
+        <v>0.8475302530143903</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8444024051905696</v>
+        <v>0.8553599574460465</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.8492414218730535</v>
+        <v>0.864706418121482</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8532980594220237</v>
+        <v>0.8752839746350628</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8542315446807778</v>
+        <v>0.8761471573122042</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8567405485444484</v>
+        <v>0.8775723335011567</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8508416442902685</v>
+        <v>0.8733563292420227</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46402</v>
       </c>
       <c r="B86">
-        <v>0.8401953942902686</v>
+        <v>0.8689035813990172</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,682 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>45814</v>
       </c>
       <c r="B2">
-        <v>0.829295</v>
+        <v>0.8234</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>45821</v>
       </c>
       <c r="B3">
-        <v>0.8300278908060462</v>
+        <v>0.7825370012221513</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>45828</v>
       </c>
       <c r="B4">
-        <v>0.8299626835302838</v>
+        <v>0.7814839200291178</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>45835</v>
       </c>
       <c r="B5">
-        <v>0.8304556503065816</v>
+        <v>0.781652262081714</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>45842</v>
       </c>
       <c r="B6">
-        <v>0.8312985415704889</v>
+        <v>0.7817625087993219</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.8330937407287253</v>
+        <v>0.788618130232736</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.8366092560206855</v>
+        <v>0.7919177056559423</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.8406817816161876</v>
+        <v>0.7912801187861906</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.8440911571064706</v>
+        <v>0.7926414854990083</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.8468363191544779</v>
+        <v>0.7913141410096025</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.8450942723399908</v>
+        <v>0.789860719397103</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.8425974482810044</v>
+        <v>0.7882834461857817</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.8413091374193675</v>
+        <v>0.7872018321588415</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B15">
+        <v>0.7892020685537214</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B16">
+        <v>0.7944835350804863</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B17">
+        <v>0.7968988051798551</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B18">
+        <v>0.7993260855239268</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B19">
+        <v>0.800162533114096</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B20">
+        <v>0.7986740381347712</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B21">
+        <v>0.7992794354084907</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B22">
+        <v>0.8039644313179624</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B23">
+        <v>0.8095921829119637</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B24">
+        <v>0.8157509707304769</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B25">
+        <v>0.8221521525019301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B26">
+        <v>0.8229338034600207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B27">
+        <v>0.8188160044783641</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B28">
+        <v>0.8153733531458784</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B29">
+        <v>0.8140487099994488</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B30">
+        <v>0.8124791608164776</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B31">
+        <v>0.8123826410605754</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B32">
+        <v>0.8176347679402511</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B33">
+        <v>0.8233586102184611</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B34">
+        <v>0.8302681944863823</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B35">
+        <v>0.8349737951987921</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B36">
+        <v>0.8201685709440848</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B37">
+        <v>0.8219901313039997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B38">
+        <v>0.8094651121627678</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B39">
+        <v>0.8013279566915819</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B40">
+        <v>0.7941834990590391</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B41">
+        <v>0.7846331021950301</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B42">
+        <v>0.7688685545081815</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B43">
+        <v>0.7665826749104553</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B44">
+        <v>0.7583506760832961</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B45">
+        <v>0.7475010841834335</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B46">
+        <v>0.738486452809417</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B47">
+        <v>0.7287735974725265</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B48">
+        <v>0.7326046069370236</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B49">
+        <v>0.7379577815417213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B50">
+        <v>0.7475973646625862</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B51">
+        <v>0.7563822704576029</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B52">
+        <v>0.7727446688614408</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B53">
+        <v>0.7771774301406864</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B54">
+        <v>0.7776894160885605</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B55">
+        <v>0.7831829963977346</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B56">
+        <v>0.7885371875458493</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B57">
+        <v>0.7923559995694035</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B58">
+        <v>0.7892858517044147</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B59">
+        <v>0.791877053993434</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B60">
+        <v>0.7971450662934005</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B61">
+        <v>0.8006922939131631</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B62">
+        <v>0.8040671625749805</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B63">
+        <v>0.8067912553744445</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B64">
+        <v>0.8090339392042666</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B65">
+        <v>0.8095765641010011</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B66">
+        <v>0.8094450305559862</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B67">
+        <v>0.8097468353103848</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B68">
+        <v>0.810372133453956</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B69">
+        <v>0.8143032228394518</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B70">
+        <v>0.8195259095687636</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B71">
+        <v>0.8243243772157154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B72">
+        <v>0.8285385116203468</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B73">
+        <v>0.8322192310674899</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B74">
+        <v>0.8359820933998989</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B75">
+        <v>0.837197641981736</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B76">
+        <v>0.8379107081990032</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B77">
+        <v>0.839118688257169</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B78">
+        <v>0.8407233292805535</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B79">
+        <v>0.8469939203573132</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B80">
+        <v>0.8545888678484146</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B81">
+        <v>0.863588129619497</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B82">
+        <v>0.8737108468519926</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B83">
+        <v>0.8744148971506158</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B84">
+        <v>0.8755187231462009</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>0.842482242907634</v>
+      <c r="B85">
+        <v>0.8713304620891354</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B86">
+        <v>0.8667708660608427</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCHF_forecast.xlsx
+++ b/public/data/files/USDCHF_forecast.xlsx
@@ -442,7 +442,7 @@
         <v>45849</v>
       </c>
       <c r="B7">
-        <v>0.788618130232736</v>
+        <v>0.7886175314428605</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -450,7 +450,7 @@
         <v>45856</v>
       </c>
       <c r="B8">
-        <v>0.7919177056559423</v>
+        <v>0.791916547300165</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -458,7 +458,7 @@
         <v>45863</v>
       </c>
       <c r="B9">
-        <v>0.7912801187861906</v>
+        <v>0.791278942519872</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -466,7 +466,7 @@
         <v>45870</v>
       </c>
       <c r="B10">
-        <v>0.7926414854990083</v>
+        <v>0.7926396233060788</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -474,7 +474,7 @@
         <v>45877</v>
       </c>
       <c r="B11">
-        <v>0.7913141410096025</v>
+        <v>0.7913122243628948</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -482,7 +482,7 @@
         <v>45884</v>
       </c>
       <c r="B12">
-        <v>0.789860719397103</v>
+        <v>0.7898587737464819</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -490,7 +490,7 @@
         <v>45891</v>
       </c>
       <c r="B13">
-        <v>0.7882834461857817</v>
+        <v>0.7882815103410158</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -498,7 +498,7 @@
         <v>45898</v>
       </c>
       <c r="B14">
-        <v>0.7872018321588415</v>
+        <v>0.787199931980282</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -506,7 +506,7 @@
         <v>45905</v>
       </c>
       <c r="B15">
-        <v>0.7892020685537214</v>
+        <v>0.7891998349103124</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -514,7 +514,7 @@
         <v>45912</v>
       </c>
       <c r="B16">
-        <v>0.7944835350804863</v>
+        <v>0.7944825034657998</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -522,7 +522,7 @@
         <v>45919</v>
       </c>
       <c r="B17">
-        <v>0.7968988051798551</v>
+        <v>0.7968977106337718</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -530,7 +530,7 @@
         <v>45926</v>
       </c>
       <c r="B18">
-        <v>0.7993260855239268</v>
+        <v>0.7993249659105479</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -538,7 +538,7 @@
         <v>45933</v>
       </c>
       <c r="B19">
-        <v>0.800162533114096</v>
+        <v>0.8001619974542347</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -546,7 +546,7 @@
         <v>45940</v>
       </c>
       <c r="B20">
-        <v>0.7986740381347712</v>
+        <v>0.7986743930164723</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -554,7 +554,7 @@
         <v>45947</v>
       </c>
       <c r="B21">
-        <v>0.7992794354084907</v>
+        <v>0.799280136777026</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -562,7 +562,7 @@
         <v>45954</v>
       </c>
       <c r="B22">
-        <v>0.8039644313179624</v>
+        <v>0.8039640748071499</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -570,7 +570,7 @@
         <v>45961</v>
       </c>
       <c r="B23">
-        <v>0.8095921829119637</v>
+        <v>0.8095907197590728</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -578,7 +578,7 @@
         <v>45968</v>
       </c>
       <c r="B24">
-        <v>0.8157509707304769</v>
+        <v>0.8157489408812216</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -586,7 +586,7 @@
         <v>45975</v>
       </c>
       <c r="B25">
-        <v>0.8221521525019301</v>
+        <v>0.8221505186588631</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -594,7 +594,7 @@
         <v>45982</v>
       </c>
       <c r="B26">
-        <v>0.8229338034600207</v>
+        <v>0.8229334215060087</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -602,7 +602,7 @@
         <v>45989</v>
       </c>
       <c r="B27">
-        <v>0.8188160044783641</v>
+        <v>0.8188175773721529</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -610,7 +610,7 @@
         <v>45996</v>
       </c>
       <c r="B28">
-        <v>0.8153733531458784</v>
+        <v>0.8153755478828302</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -618,7 +618,7 @@
         <v>46003</v>
       </c>
       <c r="B29">
-        <v>0.8140487099994488</v>
+        <v>0.8140528223737293</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -626,7 +626,7 @@
         <v>46010</v>
       </c>
       <c r="B30">
-        <v>0.8124791608164776</v>
+        <v>0.8124857903249945</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -634,7 +634,7 @@
         <v>46017</v>
       </c>
       <c r="B31">
-        <v>0.8123826410605754</v>
+        <v>0.8123911439007331</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -642,7 +642,7 @@
         <v>46024</v>
       </c>
       <c r="B32">
-        <v>0.8176347679402511</v>
+        <v>0.8176452313101066</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -650,7 +650,7 @@
         <v>46031</v>
       </c>
       <c r="B33">
-        <v>0.8233586102184611</v>
+        <v>0.8233703090292825</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -658,7 +658,7 @@
         <v>46038</v>
       </c>
       <c r="B34">
-        <v>0.8302681944863823</v>
+        <v>0.8302812128023094</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -666,7 +666,7 @@
         <v>46045</v>
       </c>
       <c r="B35">
-        <v>0.8349737951987921</v>
+        <v>0.834988273521009</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -674,7 +674,7 @@
         <v>46052</v>
       </c>
       <c r="B36">
-        <v>0.8201685709440848</v>
+        <v>0.8201851568016368</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -682,7 +682,7 @@
         <v>46059</v>
       </c>
       <c r="B37">
-        <v>0.8219901313039997</v>
+        <v>0.8220066846576993</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -690,7 +690,7 @@
         <v>46066</v>
       </c>
       <c r="B38">
-        <v>0.8094651121627678</v>
+        <v>0.8094831896204746</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -698,7 +698,7 @@
         <v>46073</v>
       </c>
       <c r="B39">
-        <v>0.8013279566915819</v>
+        <v>0.8013450145929404</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -706,7 +706,7 @@
         <v>46080</v>
       </c>
       <c r="B40">
-        <v>0.7941834990590391</v>
+        <v>0.7942031935704983</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -714,7 +714,7 @@
         <v>46087</v>
       </c>
       <c r="B41">
-        <v>0.7846331021950301</v>
+        <v>0.784654287434872</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -722,7 +722,7 @@
         <v>46094</v>
       </c>
       <c r="B42">
-        <v>0.7688685545081815</v>
+        <v>0.7688769634573666</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>46101</v>
       </c>
       <c r="B43">
-        <v>0.7665826749104553</v>
+        <v>0.7665886065556767</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>46108</v>
       </c>
       <c r="B44">
-        <v>0.7583506760832961</v>
+        <v>0.7583510520395051</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>46115</v>
       </c>
       <c r="B45">
-        <v>0.7475010841834335</v>
+        <v>0.747493118346656</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>46122</v>
       </c>
       <c r="B46">
-        <v>0.738486452809417</v>
+        <v>0.7384736506297745</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>46129</v>
       </c>
       <c r="B47">
-        <v>0.7287735974725265</v>
+        <v>0.7287552601568896</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>46136</v>
       </c>
       <c r="B48">
-        <v>0.7326046069370236</v>
+        <v>0.7325740250870162</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>46143</v>
       </c>
       <c r="B49">
-        <v>0.7379577815417213</v>
+        <v>0.7379251359970889</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>46150</v>
       </c>
       <c r="B50">
-        <v>0.7475973646625862</v>
+        <v>0.7475675360322931</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>46157</v>
       </c>
       <c r="B51">
-        <v>0.7563822704576029</v>
+        <v>0.7563531994683892</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>46164</v>
       </c>
       <c r="B52">
-        <v>0.7727446688614408</v>
+        <v>0.7727319087570264</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>46171</v>
       </c>
       <c r="B53">
-        <v>0.7771774301406864</v>
+        <v>0.7771690483987479</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>46178</v>
       </c>
       <c r="B54">
-        <v>0.7776894160885605</v>
+        <v>0.7776792972296679</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>46185</v>
       </c>
       <c r="B55">
-        <v>0.7831829963977346</v>
+        <v>0.7831773419323769</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>46192</v>
       </c>
       <c r="B56">
-        <v>0.7885371875458493</v>
+        <v>0.78853588120141</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>46199</v>
       </c>
       <c r="B57">
-        <v>0.7923559995694035</v>
+        <v>0.7923566590794139</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>46206</v>
       </c>
       <c r="B58">
-        <v>0.7892858517044147</v>
+        <v>0.789282076263659</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>46213</v>
       </c>
       <c r="B59">
-        <v>0.791877053993434</v>
+        <v>0.7918708289504992</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>46220</v>
       </c>
       <c r="B60">
-        <v>0.7971450662934005</v>
+        <v>0.7971339867326025</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>46227</v>
       </c>
       <c r="B61">
-        <v>0.8006922939131631</v>
+        <v>0.8006787467045233</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>46234</v>
       </c>
       <c r="B62">
-        <v>0.8040671625749805</v>
+        <v>0.8040530125063274</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>46241</v>
       </c>
       <c r="B63">
-        <v>0.8067912553744445</v>
+        <v>0.806778158979587</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46248</v>
       </c>
       <c r="B64">
-        <v>0.8090339392042666</v>
+        <v>0.8090227515519697</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46255</v>
       </c>
       <c r="B65">
-        <v>0.8095765641010011</v>
+        <v>0.8095716130819128</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46262</v>
       </c>
       <c r="B66">
-        <v>0.8094450305559862</v>
+        <v>0.8094470191960492</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46269</v>
       </c>
       <c r="B67">
-        <v>0.8097468353103848</v>
+        <v>0.8097498824916223</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46276</v>
       </c>
       <c r="B68">
-        <v>0.810372133453956</v>
+        <v>0.8103741880734837</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46283</v>
       </c>
       <c r="B69">
-        <v>0.8143032228394518</v>
+        <v>0.8143049865710417</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46290</v>
       </c>
       <c r="B70">
-        <v>0.8195259095687636</v>
+        <v>0.8195295958677753</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46297</v>
       </c>
       <c r="B71">
-        <v>0.8243243772157154</v>
+        <v>0.8243254386827261</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46304</v>
       </c>
       <c r="B72">
-        <v>0.8285385116203468</v>
+        <v>0.8285359367445633</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46311</v>
       </c>
       <c r="B73">
-        <v>0.8322192310674899</v>
+        <v>0.8319988291610561</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46318</v>
       </c>
       <c r="B74">
-        <v>0.8359820933998989</v>
+        <v>0.8356478397696674</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46325</v>
       </c>
       <c r="B75">
-        <v>0.837197641981736</v>
+        <v>0.8367891754748605</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46332</v>
       </c>
       <c r="B76">
-        <v>0.8379107081990032</v>
+        <v>0.8374399623465889</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46339</v>
       </c>
       <c r="B77">
-        <v>0.839118688257169</v>
+        <v>0.8385875152101907</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46346</v>
       </c>
       <c r="B78">
-        <v>0.8407233292805535</v>
+        <v>0.8401198148798822</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46353</v>
       </c>
       <c r="B79">
-        <v>0.8469939203573132</v>
+        <v>0.846172467101669</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46360</v>
       </c>
       <c r="B80">
-        <v>0.8545888678484146</v>
+        <v>0.8534768380081874</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46367</v>
       </c>
       <c r="B81">
-        <v>0.863588129619497</v>
+        <v>0.8620630461853667</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46374</v>
       </c>
       <c r="B82">
-        <v>0.8737108468519926</v>
+        <v>0.8716395426983692</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46381</v>
       </c>
       <c r="B83">
-        <v>0.8744148971506158</v>
+        <v>0.8720318016745178</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46388</v>
       </c>
       <c r="B84">
-        <v>0.8755187231462009</v>
+        <v>0.8725857752746572</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46395</v>
       </c>
       <c r="B85">
-        <v>0.8713304620891354</v>
+        <v>0.8678701972714362</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46402</v>
       </c>
       <c r="B86">
-        <v>0.8667708660608427</v>
+        <v>0.8613264034341083</v>
       </c>
     </row>
   </sheetData>
